--- a/Irish Competitions 2026 Batting stats.xlsx
+++ b/Irish Competitions 2026 Batting stats.xlsx
@@ -14,9 +14,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="Irish_Competitions_2026_Batting_stats_up_to_end_of_May_2026" localSheetId="0">Sheet1!$A$1:$T$596</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,39 +23,8 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Irish Competitions 2026 Batting stats up to end of May 2026" type="6" refreshedVersion="6" background="1" saveData="1">
-    <textPr codePage="850" sourceFile="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Irish Cup &amp; National Cup matches-\Irish Competitions 2026 Batting stats up to end of May 2026.csv" comma="1">
-      <textFields count="20">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1958" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="776">
   <si>
     <t>Group</t>
   </si>
@@ -2380,6 +2346,12 @@
   </si>
   <si>
     <t>Ross Waite</t>
+  </si>
+  <si>
+    <t>Leinster 1st XI v CSNI 1st XI, Rathmines - 19 July 2026</t>
+  </si>
+  <si>
+    <t>89*</t>
   </si>
 </sst>
 </file>
@@ -2432,10 +2404,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Irish Competitions 2026 Batting stats up to end of May 2026" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2701,7 +2669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T907"/>
+  <dimension ref="A1:T918"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -57178,6 +57146,628 @@
         <v>0</v>
       </c>
     </row>
+    <row r="908" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A908" t="s">
+        <v>774</v>
+      </c>
+      <c r="B908" t="s">
+        <v>359</v>
+      </c>
+      <c r="C908">
+        <v>1</v>
+      </c>
+      <c r="D908">
+        <v>0</v>
+      </c>
+      <c r="E908">
+        <v>0</v>
+      </c>
+      <c r="F908">
+        <v>0</v>
+      </c>
+      <c r="I908">
+        <v>0</v>
+      </c>
+      <c r="J908">
+        <v>0</v>
+      </c>
+      <c r="L908">
+        <v>0</v>
+      </c>
+      <c r="M908">
+        <v>0</v>
+      </c>
+      <c r="N908">
+        <v>0</v>
+      </c>
+      <c r="O908">
+        <v>0</v>
+      </c>
+      <c r="P908">
+        <v>0</v>
+      </c>
+      <c r="Q908">
+        <v>0</v>
+      </c>
+      <c r="R908">
+        <v>0</v>
+      </c>
+      <c r="S908">
+        <v>0</v>
+      </c>
+      <c r="T908">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A909" t="s">
+        <v>774</v>
+      </c>
+      <c r="B909" t="s">
+        <v>350</v>
+      </c>
+      <c r="C909">
+        <v>1</v>
+      </c>
+      <c r="D909">
+        <v>0</v>
+      </c>
+      <c r="E909">
+        <v>0</v>
+      </c>
+      <c r="F909">
+        <v>0</v>
+      </c>
+      <c r="I909">
+        <v>0</v>
+      </c>
+      <c r="J909">
+        <v>0</v>
+      </c>
+      <c r="L909">
+        <v>0</v>
+      </c>
+      <c r="M909">
+        <v>0</v>
+      </c>
+      <c r="N909">
+        <v>0</v>
+      </c>
+      <c r="O909">
+        <v>0</v>
+      </c>
+      <c r="P909">
+        <v>0</v>
+      </c>
+      <c r="Q909">
+        <v>0</v>
+      </c>
+      <c r="R909">
+        <v>0</v>
+      </c>
+      <c r="S909">
+        <v>0</v>
+      </c>
+      <c r="T909">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="910" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A910" t="s">
+        <v>774</v>
+      </c>
+      <c r="B910" t="s">
+        <v>356</v>
+      </c>
+      <c r="C910">
+        <v>1</v>
+      </c>
+      <c r="D910">
+        <v>1</v>
+      </c>
+      <c r="E910">
+        <v>0</v>
+      </c>
+      <c r="F910">
+        <v>69</v>
+      </c>
+      <c r="G910">
+        <v>69</v>
+      </c>
+      <c r="H910">
+        <v>69</v>
+      </c>
+      <c r="I910">
+        <v>1</v>
+      </c>
+      <c r="J910">
+        <v>0</v>
+      </c>
+      <c r="K910">
+        <v>104.55</v>
+      </c>
+      <c r="L910">
+        <v>66</v>
+      </c>
+      <c r="M910">
+        <v>34</v>
+      </c>
+      <c r="N910">
+        <v>11</v>
+      </c>
+      <c r="O910">
+        <v>0</v>
+      </c>
+      <c r="P910">
+        <v>28.51</v>
+      </c>
+      <c r="Q910">
+        <v>0</v>
+      </c>
+      <c r="R910">
+        <v>0</v>
+      </c>
+      <c r="S910">
+        <v>0</v>
+      </c>
+      <c r="T910">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>774</v>
+      </c>
+      <c r="B911" t="s">
+        <v>360</v>
+      </c>
+      <c r="C911">
+        <v>1</v>
+      </c>
+      <c r="D911">
+        <v>0</v>
+      </c>
+      <c r="E911">
+        <v>0</v>
+      </c>
+      <c r="F911">
+        <v>0</v>
+      </c>
+      <c r="I911">
+        <v>0</v>
+      </c>
+      <c r="J911">
+        <v>0</v>
+      </c>
+      <c r="L911">
+        <v>0</v>
+      </c>
+      <c r="M911">
+        <v>0</v>
+      </c>
+      <c r="N911">
+        <v>0</v>
+      </c>
+      <c r="O911">
+        <v>0</v>
+      </c>
+      <c r="P911">
+        <v>0</v>
+      </c>
+      <c r="Q911">
+        <v>0</v>
+      </c>
+      <c r="R911">
+        <v>0</v>
+      </c>
+      <c r="S911">
+        <v>0</v>
+      </c>
+      <c r="T911">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>774</v>
+      </c>
+      <c r="B912" t="s">
+        <v>351</v>
+      </c>
+      <c r="C912">
+        <v>1</v>
+      </c>
+      <c r="D912">
+        <v>0</v>
+      </c>
+      <c r="E912">
+        <v>0</v>
+      </c>
+      <c r="F912">
+        <v>0</v>
+      </c>
+      <c r="I912">
+        <v>0</v>
+      </c>
+      <c r="J912">
+        <v>0</v>
+      </c>
+      <c r="L912">
+        <v>0</v>
+      </c>
+      <c r="M912">
+        <v>0</v>
+      </c>
+      <c r="N912">
+        <v>0</v>
+      </c>
+      <c r="O912">
+        <v>0</v>
+      </c>
+      <c r="P912">
+        <v>0</v>
+      </c>
+      <c r="Q912">
+        <v>0</v>
+      </c>
+      <c r="R912">
+        <v>0</v>
+      </c>
+      <c r="S912">
+        <v>0</v>
+      </c>
+      <c r="T912">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>774</v>
+      </c>
+      <c r="B913" t="s">
+        <v>349</v>
+      </c>
+      <c r="C913">
+        <v>1</v>
+      </c>
+      <c r="D913">
+        <v>0</v>
+      </c>
+      <c r="E913">
+        <v>0</v>
+      </c>
+      <c r="F913">
+        <v>0</v>
+      </c>
+      <c r="I913">
+        <v>0</v>
+      </c>
+      <c r="J913">
+        <v>0</v>
+      </c>
+      <c r="L913">
+        <v>0</v>
+      </c>
+      <c r="M913">
+        <v>0</v>
+      </c>
+      <c r="N913">
+        <v>0</v>
+      </c>
+      <c r="O913">
+        <v>0</v>
+      </c>
+      <c r="P913">
+        <v>0</v>
+      </c>
+      <c r="Q913">
+        <v>1</v>
+      </c>
+      <c r="R913">
+        <v>0</v>
+      </c>
+      <c r="S913">
+        <v>0</v>
+      </c>
+      <c r="T913">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>774</v>
+      </c>
+      <c r="B914" t="s">
+        <v>366</v>
+      </c>
+      <c r="C914">
+        <v>1</v>
+      </c>
+      <c r="D914">
+        <v>1</v>
+      </c>
+      <c r="E914">
+        <v>0</v>
+      </c>
+      <c r="F914">
+        <v>38</v>
+      </c>
+      <c r="G914">
+        <v>38</v>
+      </c>
+      <c r="H914">
+        <v>38</v>
+      </c>
+      <c r="I914">
+        <v>0</v>
+      </c>
+      <c r="J914">
+        <v>0</v>
+      </c>
+      <c r="K914">
+        <v>84.44</v>
+      </c>
+      <c r="L914">
+        <v>45</v>
+      </c>
+      <c r="M914">
+        <v>30</v>
+      </c>
+      <c r="N914">
+        <v>6</v>
+      </c>
+      <c r="O914">
+        <v>1</v>
+      </c>
+      <c r="P914">
+        <v>15.7</v>
+      </c>
+      <c r="Q914">
+        <v>0</v>
+      </c>
+      <c r="R914">
+        <v>0</v>
+      </c>
+      <c r="S914">
+        <v>0</v>
+      </c>
+      <c r="T914">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A915" t="s">
+        <v>774</v>
+      </c>
+      <c r="B915" t="s">
+        <v>363</v>
+      </c>
+      <c r="C915">
+        <v>1</v>
+      </c>
+      <c r="D915">
+        <v>1</v>
+      </c>
+      <c r="E915">
+        <v>1</v>
+      </c>
+      <c r="F915">
+        <v>8</v>
+      </c>
+      <c r="H915" t="s">
+        <v>83</v>
+      </c>
+      <c r="I915">
+        <v>0</v>
+      </c>
+      <c r="J915">
+        <v>0</v>
+      </c>
+      <c r="K915">
+        <v>114.29</v>
+      </c>
+      <c r="L915">
+        <v>7</v>
+      </c>
+      <c r="M915">
+        <v>4</v>
+      </c>
+      <c r="N915">
+        <v>0</v>
+      </c>
+      <c r="O915">
+        <v>1</v>
+      </c>
+      <c r="P915">
+        <v>3.31</v>
+      </c>
+      <c r="Q915">
+        <v>0</v>
+      </c>
+      <c r="R915">
+        <v>0</v>
+      </c>
+      <c r="S915">
+        <v>0</v>
+      </c>
+      <c r="T915">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A916" t="s">
+        <v>774</v>
+      </c>
+      <c r="B916" t="s">
+        <v>352</v>
+      </c>
+      <c r="C916">
+        <v>1</v>
+      </c>
+      <c r="D916">
+        <v>1</v>
+      </c>
+      <c r="E916">
+        <v>0</v>
+      </c>
+      <c r="F916">
+        <v>15</v>
+      </c>
+      <c r="G916">
+        <v>15</v>
+      </c>
+      <c r="H916">
+        <v>15</v>
+      </c>
+      <c r="I916">
+        <v>0</v>
+      </c>
+      <c r="J916">
+        <v>0</v>
+      </c>
+      <c r="K916">
+        <v>51.72</v>
+      </c>
+      <c r="L916">
+        <v>29</v>
+      </c>
+      <c r="M916">
+        <v>24</v>
+      </c>
+      <c r="N916">
+        <v>3</v>
+      </c>
+      <c r="O916">
+        <v>0</v>
+      </c>
+      <c r="P916">
+        <v>6.2</v>
+      </c>
+      <c r="Q916">
+        <v>2</v>
+      </c>
+      <c r="R916">
+        <v>0</v>
+      </c>
+      <c r="S916">
+        <v>0</v>
+      </c>
+      <c r="T916">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A917" t="s">
+        <v>774</v>
+      </c>
+      <c r="B917" t="s">
+        <v>642</v>
+      </c>
+      <c r="C917">
+        <v>1</v>
+      </c>
+      <c r="D917">
+        <v>1</v>
+      </c>
+      <c r="E917">
+        <v>1</v>
+      </c>
+      <c r="F917">
+        <v>89</v>
+      </c>
+      <c r="H917" t="s">
+        <v>775</v>
+      </c>
+      <c r="I917">
+        <v>1</v>
+      </c>
+      <c r="J917">
+        <v>0</v>
+      </c>
+      <c r="K917">
+        <v>103.49</v>
+      </c>
+      <c r="L917">
+        <v>86</v>
+      </c>
+      <c r="M917">
+        <v>50</v>
+      </c>
+      <c r="N917">
+        <v>13</v>
+      </c>
+      <c r="O917">
+        <v>2</v>
+      </c>
+      <c r="P917">
+        <v>36.78</v>
+      </c>
+      <c r="Q917">
+        <v>0</v>
+      </c>
+      <c r="R917">
+        <v>1</v>
+      </c>
+      <c r="S917">
+        <v>0</v>
+      </c>
+      <c r="T917">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A918" t="s">
+        <v>774</v>
+      </c>
+      <c r="B918" t="s">
+        <v>365</v>
+      </c>
+      <c r="C918">
+        <v>1</v>
+      </c>
+      <c r="D918">
+        <v>0</v>
+      </c>
+      <c r="E918">
+        <v>0</v>
+      </c>
+      <c r="F918">
+        <v>0</v>
+      </c>
+      <c r="I918">
+        <v>0</v>
+      </c>
+      <c r="J918">
+        <v>0</v>
+      </c>
+      <c r="L918">
+        <v>0</v>
+      </c>
+      <c r="M918">
+        <v>0</v>
+      </c>
+      <c r="N918">
+        <v>0</v>
+      </c>
+      <c r="O918">
+        <v>0</v>
+      </c>
+      <c r="P918">
+        <v>0</v>
+      </c>
+      <c r="Q918">
+        <v>1</v>
+      </c>
+      <c r="R918">
+        <v>0</v>
+      </c>
+      <c r="S918">
+        <v>0</v>
+      </c>
+      <c r="T918">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Batting stats.xlsx
+++ b/Irish Competitions 2026 Batting stats.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="775">
   <si>
     <t>Group</t>
   </si>
@@ -1770,9 +1770,6 @@
   </si>
   <si>
     <t>Ethan Wilson</t>
-  </si>
-  <si>
-    <t>Joshua Wilson</t>
   </si>
   <si>
     <t>Lisburn 2nd XI v Donemana 2nd XI, Wallace Park - 31 May 2026</t>
@@ -3071,7 +3068,7 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3195,7 +3192,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3747,7 +3744,7 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -3806,7 +3803,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5373,7 +5370,7 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -6255,7 +6252,7 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -6503,7 +6500,7 @@
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6627,7 +6624,7 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6866,7 +6863,7 @@
         <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6978,7 +6975,7 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7388,7 +7385,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7509,7 +7506,7 @@
         <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7810,7 +7807,7 @@
         <v>89</v>
       </c>
       <c r="B86" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -9941,7 +9938,7 @@
         <v>133</v>
       </c>
       <c r="B121" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C121">
         <v>1</v>
@@ -14084,7 +14081,7 @@
         <v>205</v>
       </c>
       <c r="B190" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -14332,7 +14329,7 @@
         <v>205</v>
       </c>
       <c r="B194" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -14453,7 +14450,7 @@
         <v>205</v>
       </c>
       <c r="B196" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -15229,7 +15226,7 @@
         <v>226</v>
       </c>
       <c r="B209" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -18176,7 +18173,7 @@
         <v>276</v>
       </c>
       <c r="B259" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -18238,7 +18235,7 @@
         <v>276</v>
       </c>
       <c r="B260" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -20046,7 +20043,7 @@
         <v>324</v>
       </c>
       <c r="B291" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -20627,7 +20624,7 @@
         <v>324</v>
       </c>
       <c r="B301" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -21488,7 +21485,7 @@
         <v>347</v>
       </c>
       <c r="B316" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -21901,7 +21898,7 @@
         <v>347</v>
       </c>
       <c r="B323" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -22140,7 +22137,7 @@
         <v>347</v>
       </c>
       <c r="B327" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -22202,7 +22199,7 @@
         <v>347</v>
       </c>
       <c r="B328" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -23713,7 +23710,7 @@
         <v>367</v>
       </c>
       <c r="B353" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -24014,7 +24011,7 @@
         <v>390</v>
       </c>
       <c r="B358" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -24436,7 +24433,7 @@
         <v>390</v>
       </c>
       <c r="B365" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -24551,7 +24548,7 @@
         <v>390</v>
       </c>
       <c r="B367" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -25147,7 +25144,7 @@
         <v>412</v>
       </c>
       <c r="B377" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C377">
         <v>1</v>
@@ -25209,7 +25206,7 @@
         <v>412</v>
       </c>
       <c r="B378" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -25569,7 +25566,7 @@
         <v>412</v>
       </c>
       <c r="B384" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -25693,7 +25690,7 @@
         <v>412</v>
       </c>
       <c r="B386" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -26248,7 +26245,7 @@
         <v>412</v>
       </c>
       <c r="B395" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C395">
         <v>1</v>
@@ -26434,7 +26431,7 @@
         <v>412</v>
       </c>
       <c r="B398" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -26865,7 +26862,7 @@
         <v>431</v>
       </c>
       <c r="B405" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C405">
         <v>1</v>
@@ -26989,7 +26986,7 @@
         <v>431</v>
       </c>
       <c r="B407" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C407">
         <v>1</v>
@@ -27051,7 +27048,7 @@
         <v>431</v>
       </c>
       <c r="B408" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C408">
         <v>1</v>
@@ -27166,7 +27163,7 @@
         <v>431</v>
       </c>
       <c r="B410" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -27352,7 +27349,7 @@
         <v>431</v>
       </c>
       <c r="B413" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -27653,7 +27650,7 @@
         <v>431</v>
       </c>
       <c r="B418" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C418">
         <v>1</v>
@@ -28063,7 +28060,7 @@
         <v>441</v>
       </c>
       <c r="B425" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C425">
         <v>1</v>
@@ -29916,7 +29913,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C456">
         <v>1</v>
@@ -35083,7 +35080,7 @@
         <v>496</v>
       </c>
       <c r="B542" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C542">
         <v>1</v>
@@ -35331,7 +35328,7 @@
         <v>496</v>
       </c>
       <c r="B546" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C546">
         <v>1</v>
@@ -35517,7 +35514,7 @@
         <v>496</v>
       </c>
       <c r="B549" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C549">
         <v>1</v>
@@ -36134,7 +36131,7 @@
         <v>506</v>
       </c>
       <c r="B559" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C559">
         <v>1</v>
@@ -36311,7 +36308,7 @@
         <v>506</v>
       </c>
       <c r="B562" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C562">
         <v>1</v>
@@ -36730,7 +36727,7 @@
         <v>506</v>
       </c>
       <c r="B569" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C569">
         <v>1</v>
@@ -36783,7 +36780,7 @@
         <v>506</v>
       </c>
       <c r="B570" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C570">
         <v>1</v>
@@ -38480,7 +38477,7 @@
         <v>522</v>
       </c>
       <c r="B598" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C598">
         <v>1</v>
@@ -38533,7 +38530,7 @@
         <v>522</v>
       </c>
       <c r="B599" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C599">
         <v>1</v>
@@ -38592,7 +38589,7 @@
         <v>522</v>
       </c>
       <c r="B600" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C600">
         <v>1</v>
@@ -39132,7 +39129,7 @@
         <v>522</v>
       </c>
       <c r="B609" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C609">
         <v>1</v>
@@ -39247,7 +39244,7 @@
         <v>522</v>
       </c>
       <c r="B611" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C611">
         <v>1</v>
@@ -39353,7 +39350,7 @@
         <v>522</v>
       </c>
       <c r="B613" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C613">
         <v>1</v>
@@ -39530,7 +39527,7 @@
         <v>522</v>
       </c>
       <c r="B616" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C616">
         <v>1</v>
@@ -39775,7 +39772,7 @@
         <v>536</v>
       </c>
       <c r="B620" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C620">
         <v>1</v>
@@ -40011,7 +40008,7 @@
         <v>536</v>
       </c>
       <c r="B624" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C624">
         <v>1</v>
@@ -40073,7 +40070,7 @@
         <v>536</v>
       </c>
       <c r="B625" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C625">
         <v>1</v>
@@ -40188,7 +40185,7 @@
         <v>536</v>
       </c>
       <c r="B627" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C627">
         <v>1</v>
@@ -40250,7 +40247,7 @@
         <v>536</v>
       </c>
       <c r="B628" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C628">
         <v>1</v>
@@ -40610,7 +40607,7 @@
         <v>536</v>
       </c>
       <c r="B634" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C634">
         <v>1</v>
@@ -40725,7 +40722,7 @@
         <v>536</v>
       </c>
       <c r="B636" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C636">
         <v>1</v>
@@ -40778,7 +40775,7 @@
         <v>536</v>
       </c>
       <c r="B637" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C637">
         <v>1</v>
@@ -40899,7 +40896,7 @@
         <v>536</v>
       </c>
       <c r="B639" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C639">
         <v>1</v>
@@ -41392,7 +41389,7 @@
         <v>548</v>
       </c>
       <c r="B647" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C647">
         <v>1</v>
@@ -41575,7 +41572,7 @@
         <v>548</v>
       </c>
       <c r="B650" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C650">
         <v>1</v>
@@ -42009,7 +42006,7 @@
         <v>548</v>
       </c>
       <c r="B657" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C657">
         <v>1</v>
@@ -42071,7 +42068,7 @@
         <v>548</v>
       </c>
       <c r="B658" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C658">
         <v>1</v>
@@ -42257,7 +42254,7 @@
         <v>548</v>
       </c>
       <c r="B661" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C661">
         <v>1</v>
@@ -43455,7 +43452,7 @@
         <v>566</v>
       </c>
       <c r="B681" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C681">
         <v>1</v>
@@ -43679,7 +43676,7 @@
         <v>566</v>
       </c>
       <c r="B685" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C685">
         <v>1</v>
@@ -43794,7 +43791,7 @@
         <v>566</v>
       </c>
       <c r="B687" t="s">
-        <v>582</v>
+        <v>669</v>
       </c>
       <c r="C687">
         <v>1</v>
@@ -43853,10 +43850,10 @@
     </row>
     <row r="688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B688" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C688">
         <v>1</v>
@@ -43915,7 +43912,7 @@
     </row>
     <row r="689" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B689" t="s">
         <v>327</v>
@@ -43977,10 +43974,10 @@
     </row>
     <row r="690" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
+        <v>582</v>
+      </c>
+      <c r="B690" t="s">
         <v>583</v>
-      </c>
-      <c r="B690" t="s">
-        <v>584</v>
       </c>
       <c r="C690">
         <v>1</v>
@@ -44036,10 +44033,10 @@
     </row>
     <row r="691" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B691" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C691">
         <v>1</v>
@@ -44098,10 +44095,10 @@
     </row>
     <row r="692" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B692" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C692">
         <v>1</v>
@@ -44160,10 +44157,10 @@
     </row>
     <row r="693" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B693" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C693">
         <v>1</v>
@@ -44213,7 +44210,7 @@
     </row>
     <row r="694" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B694" t="s">
         <v>307</v>
@@ -44275,10 +44272,10 @@
     </row>
     <row r="695" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B695" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C695">
         <v>1</v>
@@ -44337,10 +44334,10 @@
     </row>
     <row r="696" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B696" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C696">
         <v>1</v>
@@ -44396,10 +44393,10 @@
     </row>
     <row r="697" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B697" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C697">
         <v>1</v>
@@ -44458,10 +44455,10 @@
     </row>
     <row r="698" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B698" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C698">
         <v>1</v>
@@ -44520,10 +44517,10 @@
     </row>
     <row r="699" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B699" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C699">
         <v>1</v>
@@ -44582,10 +44579,10 @@
     </row>
     <row r="700" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B700" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C700">
         <v>1</v>
@@ -44644,10 +44641,10 @@
     </row>
     <row r="701" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B701" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C701">
         <v>1</v>
@@ -44706,10 +44703,10 @@
     </row>
     <row r="702" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B702" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C702">
         <v>1</v>
@@ -44768,10 +44765,10 @@
     </row>
     <row r="703" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B703" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C703">
         <v>1</v>
@@ -44821,10 +44818,10 @@
     </row>
     <row r="704" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B704" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C704">
         <v>1</v>
@@ -44883,10 +44880,10 @@
     </row>
     <row r="705" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B705" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C705">
         <v>1</v>
@@ -44901,7 +44898,7 @@
         <v>37</v>
       </c>
       <c r="H705" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I705">
         <v>0</v>
@@ -44942,10 +44939,10 @@
     </row>
     <row r="706" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B706" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C706">
         <v>1</v>
@@ -45004,10 +45001,10 @@
     </row>
     <row r="707" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B707" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C707">
         <v>1</v>
@@ -45066,10 +45063,10 @@
     </row>
     <row r="708" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B708" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C708">
         <v>1</v>
@@ -45128,10 +45125,10 @@
     </row>
     <row r="709" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B709" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C709">
         <v>1</v>
@@ -45190,10 +45187,10 @@
     </row>
     <row r="710" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B710" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C710">
         <v>1</v>
@@ -45252,10 +45249,10 @@
     </row>
     <row r="711" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
+        <v>597</v>
+      </c>
+      <c r="B711" t="s">
         <v>598</v>
-      </c>
-      <c r="B711" t="s">
-        <v>599</v>
       </c>
       <c r="C711">
         <v>1</v>
@@ -45314,10 +45311,10 @@
     </row>
     <row r="712" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B712" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C712">
         <v>1</v>
@@ -45376,10 +45373,10 @@
     </row>
     <row r="713" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B713" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C713">
         <v>1</v>
@@ -45438,10 +45435,10 @@
     </row>
     <row r="714" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B714" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C714">
         <v>1</v>
@@ -45500,10 +45497,10 @@
     </row>
     <row r="715" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B715" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C715">
         <v>1</v>
@@ -45559,10 +45556,10 @@
     </row>
     <row r="716" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B716" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C716">
         <v>1</v>
@@ -45621,7 +45618,7 @@
     </row>
     <row r="717" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B717" t="s">
         <v>472</v>
@@ -45683,10 +45680,10 @@
     </row>
     <row r="718" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B718" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C718">
         <v>1</v>
@@ -45745,10 +45742,10 @@
     </row>
     <row r="719" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B719" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C719">
         <v>1</v>
@@ -45807,10 +45804,10 @@
     </row>
     <row r="720" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B720" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C720">
         <v>1</v>
@@ -45869,10 +45866,10 @@
     </row>
     <row r="721" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B721" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C721">
         <v>1</v>
@@ -45931,10 +45928,10 @@
     </row>
     <row r="722" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B722" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C722">
         <v>1</v>
@@ -45993,10 +45990,10 @@
     </row>
     <row r="723" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B723" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C723">
         <v>1</v>
@@ -46055,10 +46052,10 @@
     </row>
     <row r="724" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B724" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C724">
         <v>1</v>
@@ -46117,10 +46114,10 @@
     </row>
     <row r="725" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B725" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C725">
         <v>1</v>
@@ -46179,10 +46176,10 @@
     </row>
     <row r="726" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B726" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C726">
         <v>1</v>
@@ -46241,10 +46238,10 @@
     </row>
     <row r="727" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B727" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C727">
         <v>1</v>
@@ -46303,10 +46300,10 @@
     </row>
     <row r="728" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B728" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C728">
         <v>1</v>
@@ -46362,10 +46359,10 @@
     </row>
     <row r="729" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B729" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C729">
         <v>1</v>
@@ -46424,10 +46421,10 @@
     </row>
     <row r="730" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B730" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C730">
         <v>1</v>
@@ -46486,10 +46483,10 @@
     </row>
     <row r="731" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B731" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C731">
         <v>1</v>
@@ -46548,10 +46545,10 @@
     </row>
     <row r="732" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
+        <v>612</v>
+      </c>
+      <c r="B732" t="s">
         <v>613</v>
-      </c>
-      <c r="B732" t="s">
-        <v>614</v>
       </c>
       <c r="C732">
         <v>1</v>
@@ -46607,10 +46604,10 @@
     </row>
     <row r="733" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B733" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C733">
         <v>1</v>
@@ -46669,10 +46666,10 @@
     </row>
     <row r="734" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B734" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C734">
         <v>1</v>
@@ -46731,10 +46728,10 @@
     </row>
     <row r="735" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B735" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C735">
         <v>1</v>
@@ -46784,10 +46781,10 @@
     </row>
     <row r="736" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B736" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C736">
         <v>1</v>
@@ -46846,10 +46843,10 @@
     </row>
     <row r="737" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B737" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C737">
         <v>1</v>
@@ -46908,10 +46905,10 @@
     </row>
     <row r="738" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B738" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C738">
         <v>1</v>
@@ -46970,10 +46967,10 @@
     </row>
     <row r="739" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B739" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C739">
         <v>1</v>
@@ -47032,7 +47029,7 @@
     </row>
     <row r="740" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B740" t="s">
         <v>331</v>
@@ -47094,10 +47091,10 @@
     </row>
     <row r="741" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B741" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C741">
         <v>1</v>
@@ -47156,10 +47153,10 @@
     </row>
     <row r="742" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B742" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C742">
         <v>1</v>
@@ -47218,10 +47215,10 @@
     </row>
     <row r="743" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B743" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C743">
         <v>1</v>
@@ -47280,10 +47277,10 @@
     </row>
     <row r="744" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B744" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C744">
         <v>1</v>
@@ -47342,10 +47339,10 @@
     </row>
     <row r="745" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B745" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C745">
         <v>1</v>
@@ -47404,10 +47401,10 @@
     </row>
     <row r="746" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B746" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C746">
         <v>1</v>
@@ -47466,10 +47463,10 @@
     </row>
     <row r="747" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B747" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C747">
         <v>1</v>
@@ -47528,7 +47525,7 @@
     </row>
     <row r="748" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B748" t="s">
         <v>340</v>
@@ -47590,7 +47587,7 @@
     </row>
     <row r="749" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B749" t="s">
         <v>341</v>
@@ -47652,10 +47649,10 @@
     </row>
     <row r="750" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B750" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C750">
         <v>1</v>
@@ -47711,10 +47708,10 @@
     </row>
     <row r="751" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B751" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C751">
         <v>1</v>
@@ -47773,10 +47770,10 @@
     </row>
     <row r="752" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B752" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C752">
         <v>1</v>
@@ -47835,7 +47832,7 @@
     </row>
     <row r="753" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B753" t="s">
         <v>461</v>
@@ -47897,7 +47894,7 @@
     </row>
     <row r="754" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B754" t="s">
         <v>325</v>
@@ -47959,7 +47956,7 @@
     </row>
     <row r="755" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B755" t="s">
         <v>326</v>
@@ -48018,10 +48015,10 @@
     </row>
     <row r="756" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
+        <v>628</v>
+      </c>
+      <c r="B756" t="s">
         <v>629</v>
-      </c>
-      <c r="B756" t="s">
-        <v>630</v>
       </c>
       <c r="C756">
         <v>1</v>
@@ -48080,7 +48077,7 @@
     </row>
     <row r="757" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B757" t="s">
         <v>329</v>
@@ -48142,7 +48139,7 @@
     </row>
     <row r="758" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B758" t="s">
         <v>231</v>
@@ -48204,7 +48201,7 @@
     </row>
     <row r="759" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B759" t="s">
         <v>333</v>
@@ -48266,7 +48263,7 @@
     </row>
     <row r="760" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B760" t="s">
         <v>233</v>
@@ -48328,7 +48325,7 @@
     </row>
     <row r="761" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B761" t="s">
         <v>334</v>
@@ -48390,7 +48387,7 @@
     </row>
     <row r="762" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B762" t="s">
         <v>336</v>
@@ -48452,7 +48449,7 @@
     </row>
     <row r="763" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B763" t="s">
         <v>235</v>
@@ -48511,10 +48508,10 @@
     </row>
     <row r="764" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B764" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C764">
         <v>1</v>
@@ -48573,7 +48570,7 @@
     </row>
     <row r="765" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B765" t="s">
         <v>239</v>
@@ -48626,7 +48623,7 @@
     </row>
     <row r="766" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B766" t="s">
         <v>342</v>
@@ -48688,7 +48685,7 @@
     </row>
     <row r="767" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B767" t="s">
         <v>504</v>
@@ -48747,7 +48744,7 @@
     </row>
     <row r="768" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B768" t="s">
         <v>240</v>
@@ -48809,7 +48806,7 @@
     </row>
     <row r="769" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B769" t="s">
         <v>242</v>
@@ -48871,7 +48868,7 @@
     </row>
     <row r="770" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B770" t="s">
         <v>244</v>
@@ -48933,7 +48930,7 @@
     </row>
     <row r="771" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B771" t="s">
         <v>245</v>
@@ -48995,7 +48992,7 @@
     </row>
     <row r="772" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B772" t="s">
         <v>249</v>
@@ -49057,7 +49054,7 @@
     </row>
     <row r="773" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B773" t="s">
         <v>345</v>
@@ -49119,7 +49116,7 @@
     </row>
     <row r="774" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B774" t="s">
         <v>346</v>
@@ -49181,7 +49178,7 @@
     </row>
     <row r="775" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B775" t="s">
         <v>461</v>
@@ -49243,7 +49240,7 @@
     </row>
     <row r="776" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B776" t="s">
         <v>158</v>
@@ -49305,10 +49302,10 @@
     </row>
     <row r="777" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
+        <v>630</v>
+      </c>
+      <c r="B777" t="s">
         <v>631</v>
-      </c>
-      <c r="B777" t="s">
-        <v>632</v>
       </c>
       <c r="C777">
         <v>1</v>
@@ -49358,7 +49355,7 @@
     </row>
     <row r="778" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B778" t="s">
         <v>161</v>
@@ -49420,7 +49417,7 @@
     </row>
     <row r="779" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B779" t="s">
         <v>468</v>
@@ -49482,7 +49479,7 @@
     </row>
     <row r="780" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B780" t="s">
         <v>136</v>
@@ -49544,7 +49541,7 @@
     </row>
     <row r="781" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B781" t="s">
         <v>164</v>
@@ -49562,7 +49559,7 @@
         <v>13</v>
       </c>
       <c r="H781" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I781">
         <v>0</v>
@@ -49603,7 +49600,7 @@
     </row>
     <row r="782" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B782" t="s">
         <v>166</v>
@@ -49656,7 +49653,7 @@
     </row>
     <row r="783" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B783" t="s">
         <v>138</v>
@@ -49718,10 +49715,10 @@
     </row>
     <row r="784" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B784" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C784">
         <v>1</v>
@@ -49780,7 +49777,7 @@
     </row>
     <row r="785" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B785" t="s">
         <v>170</v>
@@ -49842,7 +49839,7 @@
     </row>
     <row r="786" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B786" t="s">
         <v>143</v>
@@ -49904,10 +49901,10 @@
     </row>
     <row r="787" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B787" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C787">
         <v>1</v>
@@ -49963,7 +49960,7 @@
     </row>
     <row r="788" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B788" t="s">
         <v>172</v>
@@ -50019,7 +50016,7 @@
     </row>
     <row r="789" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B789" t="s">
         <v>173</v>
@@ -50081,7 +50078,7 @@
     </row>
     <row r="790" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B790" t="s">
         <v>174</v>
@@ -50143,10 +50140,10 @@
     </row>
     <row r="791" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B791" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C791">
         <v>1</v>
@@ -50196,7 +50193,7 @@
     </row>
     <row r="792" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B792" t="s">
         <v>146</v>
@@ -50214,7 +50211,7 @@
         <v>126</v>
       </c>
       <c r="H792" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I792">
         <v>0</v>
@@ -50255,7 +50252,7 @@
     </row>
     <row r="793" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B793" t="s">
         <v>148</v>
@@ -50317,7 +50314,7 @@
     </row>
     <row r="794" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B794" t="s">
         <v>150</v>
@@ -50379,7 +50376,7 @@
     </row>
     <row r="795" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B795" t="s">
         <v>153</v>
@@ -50441,7 +50438,7 @@
     </row>
     <row r="796" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B796" t="s">
         <v>180</v>
@@ -50494,7 +50491,7 @@
     </row>
     <row r="797" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B797" t="s">
         <v>155</v>
@@ -50547,10 +50544,10 @@
     </row>
     <row r="798" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
+        <v>637</v>
+      </c>
+      <c r="B798" t="s">
         <v>638</v>
-      </c>
-      <c r="B798" t="s">
-        <v>639</v>
       </c>
       <c r="C798">
         <v>1</v>
@@ -50609,10 +50606,10 @@
     </row>
     <row r="799" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B799" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C799">
         <v>1</v>
@@ -50671,10 +50668,10 @@
     </row>
     <row r="800" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B800" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C800">
         <v>1</v>
@@ -50733,7 +50730,7 @@
     </row>
     <row r="801" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B801" t="s">
         <v>349</v>
@@ -50795,7 +50792,7 @@
     </row>
     <row r="802" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B802" t="s">
         <v>351</v>
@@ -50857,7 +50854,7 @@
     </row>
     <row r="803" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B803" t="s">
         <v>463</v>
@@ -50919,7 +50916,7 @@
     </row>
     <row r="804" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B804" t="s">
         <v>352</v>
@@ -50981,10 +50978,10 @@
     </row>
     <row r="805" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B805" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C805">
         <v>1</v>
@@ -51043,7 +51040,7 @@
     </row>
     <row r="806" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B806" t="s">
         <v>358</v>
@@ -51061,7 +51058,7 @@
         <v>13</v>
       </c>
       <c r="H806" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I806">
         <v>0</v>
@@ -51102,7 +51099,7 @@
     </row>
     <row r="807" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B807" t="s">
         <v>359</v>
@@ -51164,7 +51161,7 @@
     </row>
     <row r="808" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B808" t="s">
         <v>360</v>
@@ -51226,10 +51223,10 @@
     </row>
     <row r="809" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B809" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C809">
         <v>1</v>
@@ -51285,10 +51282,10 @@
     </row>
     <row r="810" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B810" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C810">
         <v>1</v>
@@ -51347,10 +51344,10 @@
     </row>
     <row r="811" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B811" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C811">
         <v>1</v>
@@ -51409,10 +51406,10 @@
     </row>
     <row r="812" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B812" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C812">
         <v>1</v>
@@ -51471,10 +51468,10 @@
     </row>
     <row r="813" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B813" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C813">
         <v>1</v>
@@ -51533,10 +51530,10 @@
     </row>
     <row r="814" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B814" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C814">
         <v>1</v>
@@ -51595,10 +51592,10 @@
     </row>
     <row r="815" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B815" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C815">
         <v>1</v>
@@ -51657,10 +51654,10 @@
     </row>
     <row r="816" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B816" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C816">
         <v>1</v>
@@ -51719,7 +51716,7 @@
     </row>
     <row r="817" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B817" t="s">
         <v>365</v>
@@ -51781,10 +51778,10 @@
     </row>
     <row r="818" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B818" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C818">
         <v>1</v>
@@ -51843,7 +51840,7 @@
     </row>
     <row r="819" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B819" t="s">
         <v>366</v>
@@ -51905,7 +51902,7 @@
     </row>
     <row r="820" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B820" t="s">
         <v>444</v>
@@ -51967,7 +51964,7 @@
     </row>
     <row r="821" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B821" t="s">
         <v>398</v>
@@ -52029,7 +52026,7 @@
     </row>
     <row r="822" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B822" t="s">
         <v>445</v>
@@ -52091,10 +52088,10 @@
     </row>
     <row r="823" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B823" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C823">
         <v>1</v>
@@ -52153,7 +52150,7 @@
     </row>
     <row r="824" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B824" t="s">
         <v>402</v>
@@ -52215,7 +52212,7 @@
     </row>
     <row r="825" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B825" t="s">
         <v>405</v>
@@ -52277,7 +52274,7 @@
     </row>
     <row r="826" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B826" t="s">
         <v>446</v>
@@ -52339,7 +52336,7 @@
     </row>
     <row r="827" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B827" t="s">
         <v>517</v>
@@ -52401,7 +52398,7 @@
     </row>
     <row r="828" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B828" t="s">
         <v>518</v>
@@ -52463,7 +52460,7 @@
     </row>
     <row r="829" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B829" t="s">
         <v>406</v>
@@ -52525,10 +52522,10 @@
     </row>
     <row r="830" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
+        <v>651</v>
+      </c>
+      <c r="B830" t="s">
         <v>652</v>
-      </c>
-      <c r="B830" t="s">
-        <v>653</v>
       </c>
       <c r="C830">
         <v>1</v>
@@ -52587,7 +52584,7 @@
     </row>
     <row r="831" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B831" t="s">
         <v>447</v>
@@ -52640,7 +52637,7 @@
     </row>
     <row r="832" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B832" t="s">
         <v>407</v>
@@ -52699,10 +52696,10 @@
     </row>
     <row r="833" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B833" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C833">
         <v>1</v>
@@ -52761,7 +52758,7 @@
     </row>
     <row r="834" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B834" t="s">
         <v>520</v>
@@ -52823,10 +52820,10 @@
     </row>
     <row r="835" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B835" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C835">
         <v>1</v>
@@ -52882,7 +52879,7 @@
     </row>
     <row r="836" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B836" t="s">
         <v>449</v>
@@ -52900,7 +52897,7 @@
         <v>12</v>
       </c>
       <c r="H836" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I836">
         <v>0</v>
@@ -52941,7 +52938,7 @@
     </row>
     <row r="837" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B837" t="s">
         <v>450</v>
@@ -53003,7 +53000,7 @@
     </row>
     <row r="838" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B838" t="s">
         <v>451</v>
@@ -53065,7 +53062,7 @@
     </row>
     <row r="839" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B839" t="s">
         <v>452</v>
@@ -53127,7 +53124,7 @@
     </row>
     <row r="840" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B840" t="s">
         <v>521</v>
@@ -53189,7 +53186,7 @@
     </row>
     <row r="841" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B841" t="s">
         <v>454</v>
@@ -53251,10 +53248,10 @@
     </row>
     <row r="842" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B842" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C842">
         <v>1</v>
@@ -53310,10 +53307,10 @@
     </row>
     <row r="843" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B843" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C843">
         <v>1</v>
@@ -53363,10 +53360,10 @@
     </row>
     <row r="844" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B844" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C844">
         <v>1</v>
@@ -53422,10 +53419,10 @@
     </row>
     <row r="845" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B845" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C845">
         <v>1</v>
@@ -53475,10 +53472,10 @@
     </row>
     <row r="846" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B846" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C846">
         <v>1</v>
@@ -53534,7 +53531,7 @@
     </row>
     <row r="847" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B847" t="s">
         <v>307</v>
@@ -53593,10 +53590,10 @@
     </row>
     <row r="848" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B848" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C848">
         <v>1</v>
@@ -53652,10 +53649,10 @@
     </row>
     <row r="849" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B849" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C849">
         <v>1</v>
@@ -53711,10 +53708,10 @@
     </row>
     <row r="850" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B850" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C850">
         <v>1</v>
@@ -53770,10 +53767,10 @@
     </row>
     <row r="851" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B851" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C851">
         <v>1</v>
@@ -53829,10 +53826,10 @@
     </row>
     <row r="852" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B852" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C852">
         <v>1</v>
@@ -53888,10 +53885,10 @@
     </row>
     <row r="853" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B853" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C853">
         <v>1</v>
@@ -53941,10 +53938,10 @@
     </row>
     <row r="854" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B854" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C854">
         <v>1</v>
@@ -54000,10 +53997,10 @@
     </row>
     <row r="855" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B855" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C855">
         <v>1</v>
@@ -54018,7 +54015,7 @@
         <v>52</v>
       </c>
       <c r="H855" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I855">
         <v>1</v>
@@ -54056,10 +54053,10 @@
     </row>
     <row r="856" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B856" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C856">
         <v>1</v>
@@ -54074,7 +54071,7 @@
         <v>34</v>
       </c>
       <c r="H856" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="I856">
         <v>0</v>
@@ -54112,10 +54109,10 @@
     </row>
     <row r="857" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B857" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C857">
         <v>1</v>
@@ -54168,10 +54165,10 @@
     </row>
     <row r="858" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B858" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C858">
         <v>1</v>
@@ -54227,10 +54224,10 @@
     </row>
     <row r="859" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B859" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C859">
         <v>1</v>
@@ -54286,10 +54283,10 @@
     </row>
     <row r="860" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B860" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C860">
         <v>1</v>
@@ -54304,7 +54301,7 @@
         <v>12</v>
       </c>
       <c r="H860" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I860">
         <v>0</v>
@@ -54342,10 +54339,10 @@
     </row>
     <row r="861" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B861" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C861">
         <v>1</v>
@@ -54395,10 +54392,10 @@
     </row>
     <row r="862" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B862" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C862">
         <v>1</v>
@@ -54454,10 +54451,10 @@
     </row>
     <row r="863" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B863" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C863">
         <v>1</v>
@@ -54513,10 +54510,10 @@
     </row>
     <row r="864" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B864" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C864">
         <v>1</v>
@@ -54575,10 +54572,10 @@
     </row>
     <row r="865" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B865" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C865">
         <v>1</v>
@@ -54637,7 +54634,7 @@
     </row>
     <row r="866" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B866" t="s">
         <v>526</v>
@@ -54699,7 +54696,7 @@
     </row>
     <row r="867" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B867" t="s">
         <v>572</v>
@@ -54761,10 +54758,10 @@
     </row>
     <row r="868" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
+        <v>660</v>
+      </c>
+      <c r="B868" t="s">
         <v>661</v>
-      </c>
-      <c r="B868" t="s">
-        <v>662</v>
       </c>
       <c r="C868">
         <v>1</v>
@@ -54823,10 +54820,10 @@
     </row>
     <row r="869" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B869" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C869">
         <v>1</v>
@@ -54876,10 +54873,10 @@
     </row>
     <row r="870" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B870" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C870">
         <v>1</v>
@@ -54935,10 +54932,10 @@
     </row>
     <row r="871" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B871" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C871">
         <v>1</v>
@@ -54997,10 +54994,10 @@
     </row>
     <row r="872" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B872" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C872">
         <v>1</v>
@@ -55059,7 +55056,7 @@
     </row>
     <row r="873" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B873" t="s">
         <v>531</v>
@@ -55118,7 +55115,7 @@
     </row>
     <row r="874" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B874" t="s">
         <v>574</v>
@@ -55177,10 +55174,10 @@
     </row>
     <row r="875" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B875" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C875">
         <v>1</v>
@@ -55239,10 +55236,10 @@
     </row>
     <row r="876" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B876" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C876">
         <v>1</v>
@@ -55301,10 +55298,10 @@
     </row>
     <row r="877" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B877" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C877">
         <v>1</v>
@@ -55354,10 +55351,10 @@
     </row>
     <row r="878" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B878" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C878">
         <v>1</v>
@@ -55416,10 +55413,10 @@
     </row>
     <row r="879" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B879" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C879">
         <v>1</v>
@@ -55469,10 +55466,10 @@
     </row>
     <row r="880" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B880" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C880">
         <v>1</v>
@@ -55531,7 +55528,7 @@
     </row>
     <row r="881" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B881" t="s">
         <v>533</v>
@@ -55593,7 +55590,7 @@
     </row>
     <row r="882" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B882" t="s">
         <v>578</v>
@@ -55652,7 +55649,7 @@
     </row>
     <row r="883" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B883" t="s">
         <v>579</v>
@@ -55705,7 +55702,7 @@
     </row>
     <row r="884" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B884" t="s">
         <v>580</v>
@@ -55767,10 +55764,10 @@
     </row>
     <row r="885" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B885" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C885">
         <v>1</v>
@@ -55829,7 +55826,7 @@
     </row>
     <row r="886" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B886" t="s">
         <v>551</v>
@@ -55891,7 +55888,7 @@
     </row>
     <row r="887" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B887" t="s">
         <v>484</v>
@@ -55953,10 +55950,10 @@
     </row>
     <row r="888" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B888" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C888">
         <v>1</v>
@@ -56015,10 +56012,10 @@
     </row>
     <row r="889" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B889" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C889">
         <v>1</v>
@@ -56077,10 +56074,10 @@
     </row>
     <row r="890" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B890" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C890">
         <v>1</v>
@@ -56130,10 +56127,10 @@
     </row>
     <row r="891" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
+        <v>670</v>
+      </c>
+      <c r="B891" t="s">
         <v>671</v>
-      </c>
-      <c r="B891" t="s">
-        <v>672</v>
       </c>
       <c r="C891">
         <v>1</v>
@@ -56192,10 +56189,10 @@
     </row>
     <row r="892" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B892" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C892">
         <v>1</v>
@@ -56254,7 +56251,7 @@
     </row>
     <row r="893" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B893" t="s">
         <v>542</v>
@@ -56307,10 +56304,10 @@
     </row>
     <row r="894" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B894" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C894">
         <v>1</v>
@@ -56369,7 +56366,7 @@
     </row>
     <row r="895" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B895" t="s">
         <v>291</v>
@@ -56431,7 +56428,7 @@
     </row>
     <row r="896" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B896" t="s">
         <v>558</v>
@@ -56493,10 +56490,10 @@
     </row>
     <row r="897" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B897" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C897">
         <v>1</v>
@@ -56546,10 +56543,10 @@
     </row>
     <row r="898" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B898" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C898">
         <v>1</v>
@@ -56608,10 +56605,10 @@
     </row>
     <row r="899" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B899" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C899">
         <v>1</v>
@@ -56670,10 +56667,10 @@
     </row>
     <row r="900" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B900" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C900">
         <v>1</v>
@@ -56729,7 +56726,7 @@
     </row>
     <row r="901" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B901" t="s">
         <v>559</v>
@@ -56791,7 +56788,7 @@
     </row>
     <row r="902" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B902" t="s">
         <v>297</v>
@@ -56850,7 +56847,7 @@
     </row>
     <row r="903" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B903" t="s">
         <v>271</v>
@@ -56912,10 +56909,10 @@
     </row>
     <row r="904" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B904" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C904">
         <v>1</v>
@@ -56971,7 +56968,7 @@
     </row>
     <row r="905" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B905" t="s">
         <v>562</v>
@@ -57033,10 +57030,10 @@
     </row>
     <row r="906" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B906" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C906">
         <v>1</v>
@@ -57095,7 +57092,7 @@
     </row>
     <row r="907" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B907" t="s">
         <v>299</v>
@@ -57148,7 +57145,7 @@
     </row>
     <row r="908" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B908" t="s">
         <v>359</v>
@@ -57201,7 +57198,7 @@
     </row>
     <row r="909" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B909" t="s">
         <v>350</v>
@@ -57254,7 +57251,7 @@
     </row>
     <row r="910" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B910" t="s">
         <v>356</v>
@@ -57316,7 +57313,7 @@
     </row>
     <row r="911" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B911" t="s">
         <v>360</v>
@@ -57369,7 +57366,7 @@
     </row>
     <row r="912" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B912" t="s">
         <v>351</v>
@@ -57422,7 +57419,7 @@
     </row>
     <row r="913" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B913" t="s">
         <v>349</v>
@@ -57475,7 +57472,7 @@
     </row>
     <row r="914" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B914" t="s">
         <v>366</v>
@@ -57537,7 +57534,7 @@
     </row>
     <row r="915" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B915" t="s">
         <v>363</v>
@@ -57596,7 +57593,7 @@
     </row>
     <row r="916" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B916" t="s">
         <v>352</v>
@@ -57658,10 +57655,10 @@
     </row>
     <row r="917" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B917" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C917">
         <v>1</v>
@@ -57676,7 +57673,7 @@
         <v>89</v>
       </c>
       <c r="H917" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I917">
         <v>1</v>
@@ -57717,7 +57714,7 @@
     </row>
     <row r="918" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B918" t="s">
         <v>365</v>

--- a/Irish Competitions 2026 Batting stats.xlsx
+++ b/Irish Competitions 2026 Batting stats.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="777">
   <si>
     <t>Group</t>
   </si>
@@ -2349,6 +2349,12 @@
   </si>
   <si>
     <t>89*</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v Brigade 2nd XI, Moylena - 9 August 2026</t>
+  </si>
+  <si>
+    <t>Graeme Ormiston</t>
   </si>
 </sst>
 </file>
@@ -2666,7 +2672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T918"/>
+  <dimension ref="A1:T929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -57765,6 +57771,628 @@
         <v>0</v>
       </c>
     </row>
+    <row r="919" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A919" t="s">
+        <v>775</v>
+      </c>
+      <c r="B919" t="s">
+        <v>281</v>
+      </c>
+      <c r="C919">
+        <v>1</v>
+      </c>
+      <c r="D919">
+        <v>0</v>
+      </c>
+      <c r="E919">
+        <v>0</v>
+      </c>
+      <c r="F919">
+        <v>0</v>
+      </c>
+      <c r="I919">
+        <v>0</v>
+      </c>
+      <c r="J919">
+        <v>0</v>
+      </c>
+      <c r="L919">
+        <v>0</v>
+      </c>
+      <c r="M919">
+        <v>0</v>
+      </c>
+      <c r="N919">
+        <v>0</v>
+      </c>
+      <c r="O919">
+        <v>0</v>
+      </c>
+      <c r="P919">
+        <v>0</v>
+      </c>
+      <c r="Q919">
+        <v>0</v>
+      </c>
+      <c r="R919">
+        <v>0</v>
+      </c>
+      <c r="S919">
+        <v>0</v>
+      </c>
+      <c r="T919">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="920" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A920" t="s">
+        <v>775</v>
+      </c>
+      <c r="B920" t="s">
+        <v>282</v>
+      </c>
+      <c r="C920">
+        <v>1</v>
+      </c>
+      <c r="D920">
+        <v>1</v>
+      </c>
+      <c r="E920">
+        <v>0</v>
+      </c>
+      <c r="F920">
+        <v>4</v>
+      </c>
+      <c r="G920">
+        <v>4</v>
+      </c>
+      <c r="H920">
+        <v>4</v>
+      </c>
+      <c r="I920">
+        <v>0</v>
+      </c>
+      <c r="J920">
+        <v>0</v>
+      </c>
+      <c r="K920">
+        <v>66.67</v>
+      </c>
+      <c r="L920">
+        <v>6</v>
+      </c>
+      <c r="M920">
+        <v>3</v>
+      </c>
+      <c r="N920">
+        <v>0</v>
+      </c>
+      <c r="O920">
+        <v>0</v>
+      </c>
+      <c r="P920">
+        <v>3.36</v>
+      </c>
+      <c r="Q920">
+        <v>0</v>
+      </c>
+      <c r="R920">
+        <v>0</v>
+      </c>
+      <c r="S920">
+        <v>0</v>
+      </c>
+      <c r="T920">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A921" t="s">
+        <v>775</v>
+      </c>
+      <c r="B921" t="s">
+        <v>286</v>
+      </c>
+      <c r="C921">
+        <v>1</v>
+      </c>
+      <c r="D921">
+        <v>0</v>
+      </c>
+      <c r="E921">
+        <v>0</v>
+      </c>
+      <c r="F921">
+        <v>0</v>
+      </c>
+      <c r="I921">
+        <v>0</v>
+      </c>
+      <c r="J921">
+        <v>0</v>
+      </c>
+      <c r="L921">
+        <v>0</v>
+      </c>
+      <c r="M921">
+        <v>0</v>
+      </c>
+      <c r="N921">
+        <v>0</v>
+      </c>
+      <c r="O921">
+        <v>0</v>
+      </c>
+      <c r="P921">
+        <v>0</v>
+      </c>
+      <c r="Q921">
+        <v>2</v>
+      </c>
+      <c r="R921">
+        <v>0</v>
+      </c>
+      <c r="S921">
+        <v>0</v>
+      </c>
+      <c r="T921">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A922" t="s">
+        <v>775</v>
+      </c>
+      <c r="B922" t="s">
+        <v>289</v>
+      </c>
+      <c r="C922">
+        <v>1</v>
+      </c>
+      <c r="D922">
+        <v>1</v>
+      </c>
+      <c r="E922">
+        <v>0</v>
+      </c>
+      <c r="F922">
+        <v>8</v>
+      </c>
+      <c r="G922">
+        <v>8</v>
+      </c>
+      <c r="H922">
+        <v>8</v>
+      </c>
+      <c r="I922">
+        <v>0</v>
+      </c>
+      <c r="J922">
+        <v>0</v>
+      </c>
+      <c r="K922">
+        <v>80</v>
+      </c>
+      <c r="L922">
+        <v>10</v>
+      </c>
+      <c r="M922">
+        <v>7</v>
+      </c>
+      <c r="N922">
+        <v>0</v>
+      </c>
+      <c r="O922">
+        <v>1</v>
+      </c>
+      <c r="P922">
+        <v>6.72</v>
+      </c>
+      <c r="Q922">
+        <v>1</v>
+      </c>
+      <c r="R922">
+        <v>0</v>
+      </c>
+      <c r="S922">
+        <v>0</v>
+      </c>
+      <c r="T922">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A923" t="s">
+        <v>775</v>
+      </c>
+      <c r="B923" t="s">
+        <v>571</v>
+      </c>
+      <c r="C923">
+        <v>1</v>
+      </c>
+      <c r="D923">
+        <v>1</v>
+      </c>
+      <c r="E923">
+        <v>1</v>
+      </c>
+      <c r="F923">
+        <v>64</v>
+      </c>
+      <c r="H923" t="s">
+        <v>543</v>
+      </c>
+      <c r="I923">
+        <v>1</v>
+      </c>
+      <c r="J923">
+        <v>0</v>
+      </c>
+      <c r="K923">
+        <v>139.13</v>
+      </c>
+      <c r="L923">
+        <v>46</v>
+      </c>
+      <c r="M923">
+        <v>22</v>
+      </c>
+      <c r="N923">
+        <v>3</v>
+      </c>
+      <c r="O923">
+        <v>5</v>
+      </c>
+      <c r="P923">
+        <v>53.78</v>
+      </c>
+      <c r="Q923">
+        <v>0</v>
+      </c>
+      <c r="R923">
+        <v>0</v>
+      </c>
+      <c r="S923">
+        <v>0</v>
+      </c>
+      <c r="T923">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>775</v>
+      </c>
+      <c r="B924" t="s">
+        <v>464</v>
+      </c>
+      <c r="C924">
+        <v>1</v>
+      </c>
+      <c r="D924">
+        <v>0</v>
+      </c>
+      <c r="E924">
+        <v>0</v>
+      </c>
+      <c r="F924">
+        <v>0</v>
+      </c>
+      <c r="I924">
+        <v>0</v>
+      </c>
+      <c r="J924">
+        <v>0</v>
+      </c>
+      <c r="L924">
+        <v>0</v>
+      </c>
+      <c r="M924">
+        <v>0</v>
+      </c>
+      <c r="N924">
+        <v>0</v>
+      </c>
+      <c r="O924">
+        <v>0</v>
+      </c>
+      <c r="P924">
+        <v>0</v>
+      </c>
+      <c r="Q924">
+        <v>0</v>
+      </c>
+      <c r="R924">
+        <v>0</v>
+      </c>
+      <c r="S924">
+        <v>0</v>
+      </c>
+      <c r="T924">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>775</v>
+      </c>
+      <c r="B925" t="s">
+        <v>661</v>
+      </c>
+      <c r="C925">
+        <v>1</v>
+      </c>
+      <c r="D925">
+        <v>1</v>
+      </c>
+      <c r="E925">
+        <v>0</v>
+      </c>
+      <c r="F925">
+        <v>14</v>
+      </c>
+      <c r="G925">
+        <v>14</v>
+      </c>
+      <c r="H925">
+        <v>14</v>
+      </c>
+      <c r="I925">
+        <v>0</v>
+      </c>
+      <c r="J925">
+        <v>0</v>
+      </c>
+      <c r="K925">
+        <v>127.27</v>
+      </c>
+      <c r="L925">
+        <v>11</v>
+      </c>
+      <c r="M925">
+        <v>6</v>
+      </c>
+      <c r="N925">
+        <v>3</v>
+      </c>
+      <c r="O925">
+        <v>0</v>
+      </c>
+      <c r="P925">
+        <v>11.76</v>
+      </c>
+      <c r="Q925">
+        <v>0</v>
+      </c>
+      <c r="R925">
+        <v>0</v>
+      </c>
+      <c r="S925">
+        <v>0</v>
+      </c>
+      <c r="T925">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>775</v>
+      </c>
+      <c r="B926" t="s">
+        <v>664</v>
+      </c>
+      <c r="C926">
+        <v>1</v>
+      </c>
+      <c r="D926">
+        <v>1</v>
+      </c>
+      <c r="E926">
+        <v>1</v>
+      </c>
+      <c r="F926">
+        <v>22</v>
+      </c>
+      <c r="H926" t="s">
+        <v>511</v>
+      </c>
+      <c r="I926">
+        <v>0</v>
+      </c>
+      <c r="J926">
+        <v>0</v>
+      </c>
+      <c r="K926">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="L926">
+        <v>34</v>
+      </c>
+      <c r="M926">
+        <v>20</v>
+      </c>
+      <c r="N926">
+        <v>1</v>
+      </c>
+      <c r="O926">
+        <v>1</v>
+      </c>
+      <c r="P926">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="Q926">
+        <v>0</v>
+      </c>
+      <c r="R926">
+        <v>0</v>
+      </c>
+      <c r="S926">
+        <v>0</v>
+      </c>
+      <c r="T926">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>775</v>
+      </c>
+      <c r="B927" t="s">
+        <v>667</v>
+      </c>
+      <c r="C927">
+        <v>1</v>
+      </c>
+      <c r="D927">
+        <v>0</v>
+      </c>
+      <c r="E927">
+        <v>0</v>
+      </c>
+      <c r="F927">
+        <v>0</v>
+      </c>
+      <c r="I927">
+        <v>0</v>
+      </c>
+      <c r="J927">
+        <v>0</v>
+      </c>
+      <c r="L927">
+        <v>0</v>
+      </c>
+      <c r="M927">
+        <v>0</v>
+      </c>
+      <c r="N927">
+        <v>0</v>
+      </c>
+      <c r="O927">
+        <v>0</v>
+      </c>
+      <c r="P927">
+        <v>0</v>
+      </c>
+      <c r="Q927">
+        <v>1</v>
+      </c>
+      <c r="R927">
+        <v>0</v>
+      </c>
+      <c r="S927">
+        <v>0</v>
+      </c>
+      <c r="T927">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A928" t="s">
+        <v>775</v>
+      </c>
+      <c r="B928" t="s">
+        <v>776</v>
+      </c>
+      <c r="C928">
+        <v>1</v>
+      </c>
+      <c r="D928">
+        <v>0</v>
+      </c>
+      <c r="E928">
+        <v>0</v>
+      </c>
+      <c r="F928">
+        <v>0</v>
+      </c>
+      <c r="I928">
+        <v>0</v>
+      </c>
+      <c r="J928">
+        <v>0</v>
+      </c>
+      <c r="L928">
+        <v>0</v>
+      </c>
+      <c r="M928">
+        <v>0</v>
+      </c>
+      <c r="N928">
+        <v>0</v>
+      </c>
+      <c r="O928">
+        <v>0</v>
+      </c>
+      <c r="P928">
+        <v>0</v>
+      </c>
+      <c r="Q928">
+        <v>1</v>
+      </c>
+      <c r="R928">
+        <v>0</v>
+      </c>
+      <c r="S928">
+        <v>0</v>
+      </c>
+      <c r="T928">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A929" t="s">
+        <v>775</v>
+      </c>
+      <c r="B929" t="s">
+        <v>581</v>
+      </c>
+      <c r="C929">
+        <v>1</v>
+      </c>
+      <c r="D929">
+        <v>0</v>
+      </c>
+      <c r="E929">
+        <v>0</v>
+      </c>
+      <c r="F929">
+        <v>0</v>
+      </c>
+      <c r="I929">
+        <v>0</v>
+      </c>
+      <c r="J929">
+        <v>0</v>
+      </c>
+      <c r="L929">
+        <v>0</v>
+      </c>
+      <c r="M929">
+        <v>0</v>
+      </c>
+      <c r="N929">
+        <v>0</v>
+      </c>
+      <c r="O929">
+        <v>0</v>
+      </c>
+      <c r="P929">
+        <v>0</v>
+      </c>
+      <c r="Q929">
+        <v>0</v>
+      </c>
+      <c r="R929">
+        <v>0</v>
+      </c>
+      <c r="S929">
+        <v>0</v>
+      </c>
+      <c r="T929">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Batting stats.xlsx
+++ b/Irish Competitions 2026 Batting stats.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Irish Cup &amp; National Cup &amp; Ulster Plate matches-\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E829B9B8-54F1-430A-A2A8-7CB0806B027C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21075" windowHeight="13650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="778">
   <si>
     <t>Group</t>
   </si>
@@ -2355,12 +2356,15 @@
   </si>
   <si>
     <t>Graeme Ormiston</t>
+  </si>
+  <si>
+    <t>CSNI 1st XI v Pembroke 1st XI, Castle Avenue - 16 August 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2671,8 +2675,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T929"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T940"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -58393,6 +58397,685 @@
         <v>0</v>
       </c>
     </row>
+    <row r="930" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A930" t="s">
+        <v>777</v>
+      </c>
+      <c r="B930" t="s">
+        <v>349</v>
+      </c>
+      <c r="C930">
+        <v>1</v>
+      </c>
+      <c r="D930">
+        <v>1</v>
+      </c>
+      <c r="E930">
+        <v>0</v>
+      </c>
+      <c r="F930">
+        <v>0</v>
+      </c>
+      <c r="G930">
+        <v>0</v>
+      </c>
+      <c r="H930">
+        <v>0</v>
+      </c>
+      <c r="I930">
+        <v>0</v>
+      </c>
+      <c r="J930">
+        <v>0</v>
+      </c>
+      <c r="K930">
+        <v>0</v>
+      </c>
+      <c r="L930">
+        <v>1</v>
+      </c>
+      <c r="M930">
+        <v>1</v>
+      </c>
+      <c r="N930">
+        <v>0</v>
+      </c>
+      <c r="O930">
+        <v>0</v>
+      </c>
+      <c r="P930">
+        <v>0</v>
+      </c>
+      <c r="Q930">
+        <v>1</v>
+      </c>
+      <c r="R930">
+        <v>0</v>
+      </c>
+      <c r="S930">
+        <v>0</v>
+      </c>
+      <c r="T930">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A931" t="s">
+        <v>777</v>
+      </c>
+      <c r="B931" t="s">
+        <v>350</v>
+      </c>
+      <c r="C931">
+        <v>1</v>
+      </c>
+      <c r="D931">
+        <v>1</v>
+      </c>
+      <c r="E931">
+        <v>0</v>
+      </c>
+      <c r="F931">
+        <v>6</v>
+      </c>
+      <c r="G931">
+        <v>6</v>
+      </c>
+      <c r="H931">
+        <v>6</v>
+      </c>
+      <c r="I931">
+        <v>0</v>
+      </c>
+      <c r="J931">
+        <v>0</v>
+      </c>
+      <c r="K931">
+        <v>40</v>
+      </c>
+      <c r="L931">
+        <v>15</v>
+      </c>
+      <c r="M931">
+        <v>9</v>
+      </c>
+      <c r="N931">
+        <v>0</v>
+      </c>
+      <c r="O931">
+        <v>0</v>
+      </c>
+      <c r="P931">
+        <v>3.47</v>
+      </c>
+      <c r="Q931">
+        <v>0</v>
+      </c>
+      <c r="R931">
+        <v>0</v>
+      </c>
+      <c r="S931">
+        <v>0</v>
+      </c>
+      <c r="T931">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>777</v>
+      </c>
+      <c r="B932" t="s">
+        <v>351</v>
+      </c>
+      <c r="C932">
+        <v>1</v>
+      </c>
+      <c r="D932">
+        <v>1</v>
+      </c>
+      <c r="E932">
+        <v>1</v>
+      </c>
+      <c r="F932">
+        <v>22</v>
+      </c>
+      <c r="H932" t="s">
+        <v>511</v>
+      </c>
+      <c r="I932">
+        <v>0</v>
+      </c>
+      <c r="J932">
+        <v>0</v>
+      </c>
+      <c r="K932">
+        <v>75.86</v>
+      </c>
+      <c r="L932">
+        <v>29</v>
+      </c>
+      <c r="M932">
+        <v>13</v>
+      </c>
+      <c r="N932">
+        <v>2</v>
+      </c>
+      <c r="O932">
+        <v>0</v>
+      </c>
+      <c r="P932">
+        <v>12.72</v>
+      </c>
+      <c r="Q932">
+        <v>1</v>
+      </c>
+      <c r="R932">
+        <v>0</v>
+      </c>
+      <c r="S932">
+        <v>0</v>
+      </c>
+      <c r="T932">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A933" t="s">
+        <v>777</v>
+      </c>
+      <c r="B933" t="s">
+        <v>352</v>
+      </c>
+      <c r="C933">
+        <v>1</v>
+      </c>
+      <c r="D933">
+        <v>1</v>
+      </c>
+      <c r="E933">
+        <v>0</v>
+      </c>
+      <c r="F933">
+        <v>8</v>
+      </c>
+      <c r="G933">
+        <v>8</v>
+      </c>
+      <c r="H933">
+        <v>8</v>
+      </c>
+      <c r="I933">
+        <v>0</v>
+      </c>
+      <c r="J933">
+        <v>0</v>
+      </c>
+      <c r="K933">
+        <v>50</v>
+      </c>
+      <c r="L933">
+        <v>16</v>
+      </c>
+      <c r="M933">
+        <v>12</v>
+      </c>
+      <c r="N933">
+        <v>1</v>
+      </c>
+      <c r="O933">
+        <v>0</v>
+      </c>
+      <c r="P933">
+        <v>4.62</v>
+      </c>
+      <c r="Q933">
+        <v>1</v>
+      </c>
+      <c r="R933">
+        <v>0</v>
+      </c>
+      <c r="S933">
+        <v>0</v>
+      </c>
+      <c r="T933">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>777</v>
+      </c>
+      <c r="B934" t="s">
+        <v>356</v>
+      </c>
+      <c r="C934">
+        <v>1</v>
+      </c>
+      <c r="D934">
+        <v>1</v>
+      </c>
+      <c r="E934">
+        <v>0</v>
+      </c>
+      <c r="F934">
+        <v>2</v>
+      </c>
+      <c r="G934">
+        <v>2</v>
+      </c>
+      <c r="H934">
+        <v>2</v>
+      </c>
+      <c r="I934">
+        <v>0</v>
+      </c>
+      <c r="J934">
+        <v>0</v>
+      </c>
+      <c r="K934">
+        <v>22.22</v>
+      </c>
+      <c r="L934">
+        <v>9</v>
+      </c>
+      <c r="M934">
+        <v>7</v>
+      </c>
+      <c r="N934">
+        <v>0</v>
+      </c>
+      <c r="O934">
+        <v>0</v>
+      </c>
+      <c r="P934">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="Q934">
+        <v>0</v>
+      </c>
+      <c r="R934">
+        <v>0</v>
+      </c>
+      <c r="S934">
+        <v>0</v>
+      </c>
+      <c r="T934">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>777</v>
+      </c>
+      <c r="B935" t="s">
+        <v>641</v>
+      </c>
+      <c r="C935">
+        <v>1</v>
+      </c>
+      <c r="D935">
+        <v>1</v>
+      </c>
+      <c r="E935">
+        <v>0</v>
+      </c>
+      <c r="F935">
+        <v>46</v>
+      </c>
+      <c r="G935">
+        <v>46</v>
+      </c>
+      <c r="H935">
+        <v>46</v>
+      </c>
+      <c r="I935">
+        <v>0</v>
+      </c>
+      <c r="J935">
+        <v>0</v>
+      </c>
+      <c r="K935">
+        <v>80.7</v>
+      </c>
+      <c r="L935">
+        <v>57</v>
+      </c>
+      <c r="M935">
+        <v>35</v>
+      </c>
+      <c r="N935">
+        <v>5</v>
+      </c>
+      <c r="O935">
+        <v>1</v>
+      </c>
+      <c r="P935">
+        <v>26.59</v>
+      </c>
+      <c r="Q935">
+        <v>0</v>
+      </c>
+      <c r="R935">
+        <v>0</v>
+      </c>
+      <c r="S935">
+        <v>0</v>
+      </c>
+      <c r="T935">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A936" t="s">
+        <v>777</v>
+      </c>
+      <c r="B936" t="s">
+        <v>358</v>
+      </c>
+      <c r="C936">
+        <v>1</v>
+      </c>
+      <c r="D936">
+        <v>1</v>
+      </c>
+      <c r="E936">
+        <v>0</v>
+      </c>
+      <c r="F936">
+        <v>2</v>
+      </c>
+      <c r="G936">
+        <v>2</v>
+      </c>
+      <c r="H936">
+        <v>2</v>
+      </c>
+      <c r="I936">
+        <v>0</v>
+      </c>
+      <c r="J936">
+        <v>0</v>
+      </c>
+      <c r="K936">
+        <v>20</v>
+      </c>
+      <c r="L936">
+        <v>10</v>
+      </c>
+      <c r="M936">
+        <v>8</v>
+      </c>
+      <c r="N936">
+        <v>0</v>
+      </c>
+      <c r="O936">
+        <v>0</v>
+      </c>
+      <c r="P936">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="Q936">
+        <v>0</v>
+      </c>
+      <c r="R936">
+        <v>0</v>
+      </c>
+      <c r="S936">
+        <v>0</v>
+      </c>
+      <c r="T936">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A937" t="s">
+        <v>777</v>
+      </c>
+      <c r="B937" t="s">
+        <v>359</v>
+      </c>
+      <c r="C937">
+        <v>1</v>
+      </c>
+      <c r="D937">
+        <v>1</v>
+      </c>
+      <c r="E937">
+        <v>0</v>
+      </c>
+      <c r="F937">
+        <v>21</v>
+      </c>
+      <c r="G937">
+        <v>21</v>
+      </c>
+      <c r="H937">
+        <v>21</v>
+      </c>
+      <c r="I937">
+        <v>0</v>
+      </c>
+      <c r="J937">
+        <v>0</v>
+      </c>
+      <c r="K937">
+        <v>95.45</v>
+      </c>
+      <c r="L937">
+        <v>22</v>
+      </c>
+      <c r="M937">
+        <v>13</v>
+      </c>
+      <c r="N937">
+        <v>3</v>
+      </c>
+      <c r="O937">
+        <v>0</v>
+      </c>
+      <c r="P937">
+        <v>12.14</v>
+      </c>
+      <c r="Q937">
+        <v>0</v>
+      </c>
+      <c r="R937">
+        <v>0</v>
+      </c>
+      <c r="S937">
+        <v>0</v>
+      </c>
+      <c r="T937">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A938" t="s">
+        <v>777</v>
+      </c>
+      <c r="B938" t="s">
+        <v>360</v>
+      </c>
+      <c r="C938">
+        <v>1</v>
+      </c>
+      <c r="D938">
+        <v>1</v>
+      </c>
+      <c r="E938">
+        <v>0</v>
+      </c>
+      <c r="F938">
+        <v>1</v>
+      </c>
+      <c r="G938">
+        <v>1</v>
+      </c>
+      <c r="H938">
+        <v>1</v>
+      </c>
+      <c r="I938">
+        <v>0</v>
+      </c>
+      <c r="J938">
+        <v>0</v>
+      </c>
+      <c r="K938">
+        <v>25</v>
+      </c>
+      <c r="L938">
+        <v>4</v>
+      </c>
+      <c r="M938">
+        <v>3</v>
+      </c>
+      <c r="N938">
+        <v>0</v>
+      </c>
+      <c r="O938">
+        <v>0</v>
+      </c>
+      <c r="P938">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q938">
+        <v>0</v>
+      </c>
+      <c r="R938">
+        <v>0</v>
+      </c>
+      <c r="S938">
+        <v>0</v>
+      </c>
+      <c r="T938">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A939" t="s">
+        <v>777</v>
+      </c>
+      <c r="B939" t="s">
+        <v>365</v>
+      </c>
+      <c r="C939">
+        <v>1</v>
+      </c>
+      <c r="D939">
+        <v>1</v>
+      </c>
+      <c r="E939">
+        <v>0</v>
+      </c>
+      <c r="F939">
+        <v>32</v>
+      </c>
+      <c r="G939">
+        <v>32</v>
+      </c>
+      <c r="H939">
+        <v>32</v>
+      </c>
+      <c r="I939">
+        <v>0</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="K939">
+        <v>76.19</v>
+      </c>
+      <c r="L939">
+        <v>42</v>
+      </c>
+      <c r="M939">
+        <v>24</v>
+      </c>
+      <c r="N939">
+        <v>4</v>
+      </c>
+      <c r="O939">
+        <v>0</v>
+      </c>
+      <c r="P939">
+        <v>18.5</v>
+      </c>
+      <c r="Q939">
+        <v>0</v>
+      </c>
+      <c r="R939">
+        <v>0</v>
+      </c>
+      <c r="S939">
+        <v>0</v>
+      </c>
+      <c r="T939">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A940" t="s">
+        <v>777</v>
+      </c>
+      <c r="B940" t="s">
+        <v>366</v>
+      </c>
+      <c r="C940">
+        <v>1</v>
+      </c>
+      <c r="D940">
+        <v>1</v>
+      </c>
+      <c r="E940">
+        <v>0</v>
+      </c>
+      <c r="F940">
+        <v>16</v>
+      </c>
+      <c r="G940">
+        <v>16</v>
+      </c>
+      <c r="H940">
+        <v>16</v>
+      </c>
+      <c r="I940">
+        <v>0</v>
+      </c>
+      <c r="J940">
+        <v>0</v>
+      </c>
+      <c r="K940">
+        <v>106.67</v>
+      </c>
+      <c r="L940">
+        <v>15</v>
+      </c>
+      <c r="M940">
+        <v>9</v>
+      </c>
+      <c r="N940">
+        <v>3</v>
+      </c>
+      <c r="O940">
+        <v>0</v>
+      </c>
+      <c r="P940">
+        <v>9.25</v>
+      </c>
+      <c r="Q940">
+        <v>0</v>
+      </c>
+      <c r="R940">
+        <v>0</v>
+      </c>
+      <c r="S940">
+        <v>0</v>
+      </c>
+      <c r="T940">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Batting stats.xlsx
+++ b/Irish Competitions 2026 Batting stats.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +24,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -415,109 +427,132 @@
   </sheetPr>
   <dimension ref="A1:U1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="26" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="38" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="12" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="10" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="13" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="10" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="10" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="10" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="10" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="14" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="10" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="19" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="11" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="10" bestFit="1" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Batter ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Innings</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Not Outs</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>High Score</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>50s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>100s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Strike Rate</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Balls</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Dots</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Contribution</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Catches as Keeper</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Run Outs</t>
         </is>
@@ -551,15 +586,12 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -762,15 +794,12 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
@@ -827,15 +856,12 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -892,15 +918,12 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -957,15 +980,12 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1022,15 +1042,12 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1087,15 +1104,12 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1152,15 +1166,12 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1217,7 +1228,6 @@
       <c r="G12" t="n">
         <v>25</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>25*</t>
@@ -1288,15 +1298,12 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1426,15 +1433,12 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -1491,7 +1495,6 @@
       <c r="G16" t="n">
         <v>23</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>23*</t>
@@ -1562,7 +1565,6 @@
       <c r="G17" t="n">
         <v>23</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>23*</t>
@@ -1633,15 +1635,12 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -1698,15 +1697,12 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -1763,15 +1759,12 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -1828,15 +1821,12 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -1893,15 +1883,12 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -1958,7 +1945,6 @@
       <c r="G23" t="n">
         <v>22</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>22*</t>
@@ -2773,7 +2759,6 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -2976,7 +2961,6 @@
       <c r="G37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2*</t>
@@ -3193,7 +3177,6 @@
       <c r="G40" t="n">
         <v>7</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>7*</t>
@@ -3629,7 +3612,6 @@
       <c r="G46" t="n">
         <v>28</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>28*</t>
@@ -3846,15 +3828,12 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>0</v>
       </c>
@@ -3911,7 +3890,6 @@
       <c r="G50" t="n">
         <v>14</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>14*</t>
@@ -3982,7 +3960,6 @@
       <c r="G51" t="n">
         <v>9</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>9*</t>
@@ -4199,15 +4176,12 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>0</v>
       </c>
@@ -4629,15 +4603,12 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>0</v>
       </c>
@@ -4913,15 +4884,12 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>0</v>
       </c>
@@ -5197,7 +5165,6 @@
       <c r="G68" t="n">
         <v>2</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2*</t>
@@ -5268,7 +5235,6 @@
       <c r="G69" t="n">
         <v>135</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>135*</t>
@@ -5339,15 +5305,12 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>0</v>
       </c>
@@ -5477,15 +5440,12 @@
       <c r="G72" t="n">
         <v>0</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>0</v>
       </c>
@@ -5542,15 +5502,12 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>0</v>
       </c>
@@ -5753,15 +5710,12 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>0</v>
       </c>
@@ -6037,7 +5991,6 @@
       <c r="G80" t="n">
         <v>26</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>26*</t>
@@ -6108,7 +6061,6 @@
       <c r="G81" t="n">
         <v>8</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>8*</t>
@@ -6690,15 +6642,12 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
         <v>0</v>
       </c>
@@ -6901,15 +6850,12 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>0</v>
       </c>
@@ -6966,7 +6912,6 @@
       <c r="G93" t="n">
         <v>59</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>59*</t>
@@ -7037,15 +6982,12 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>0</v>
       </c>
@@ -7102,7 +7044,6 @@
       <c r="G95" t="n">
         <v>23</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>23*</t>
@@ -7319,7 +7260,6 @@
       <c r="G98" t="n">
         <v>2</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2*</t>
@@ -7390,15 +7330,12 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
         <v>0</v>
       </c>
@@ -7601,7 +7538,6 @@
       <c r="G102" t="n">
         <v>7</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>7*</t>
@@ -7672,15 +7608,12 @@
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
       </c>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
         <v>0</v>
       </c>
@@ -8613,7 +8546,6 @@
       <c r="G116" t="n">
         <v>9</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>9*</t>
@@ -8757,15 +8689,12 @@
       <c r="G118" t="n">
         <v>0</v>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
       </c>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
         <v>0</v>
       </c>
@@ -8968,7 +8897,6 @@
       <c r="G121" t="n">
         <v>17</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>17*</t>
@@ -9477,15 +9405,12 @@
       <c r="G128" t="n">
         <v>0</v>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
         <v>0</v>
       </c>
@@ -9980,15 +9905,12 @@
       <c r="G135" t="n">
         <v>0</v>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
         <v>0</v>
       </c>
@@ -10045,15 +9967,12 @@
       <c r="G136" t="n">
         <v>0</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
         <v>0</v>
       </c>
@@ -10329,15 +10248,12 @@
       <c r="G140" t="n">
         <v>0</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
         <v>0</v>
       </c>
@@ -10467,7 +10383,6 @@
       <c r="G142" t="n">
         <v>125</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>125*</t>
@@ -10976,7 +10891,6 @@
       <c r="G149" t="n">
         <v>8</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>8*</t>
@@ -11120,15 +11034,12 @@
       <c r="G151" t="n">
         <v>0</v>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="n">
         <v>0</v>
       </c>
@@ -11185,15 +11096,12 @@
       <c r="G152" t="n">
         <v>0</v>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
       </c>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
         <v>0</v>
       </c>
@@ -11323,15 +11231,12 @@
       <c r="G154" t="n">
         <v>0</v>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
       </c>
-      <c r="L154" t="inlineStr"/>
       <c r="M154" t="n">
         <v>0</v>
       </c>
@@ -11680,15 +11585,12 @@
       <c r="G159" t="n">
         <v>0</v>
       </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
       </c>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="n">
         <v>0</v>
       </c>
@@ -11891,7 +11793,6 @@
       <c r="G162" t="n">
         <v>31</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>31*</t>
@@ -11962,15 +11863,12 @@
       <c r="G163" t="n">
         <v>0</v>
       </c>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
       </c>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="n">
         <v>0</v>
       </c>
@@ -12027,15 +11925,12 @@
       <c r="G164" t="n">
         <v>0</v>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
-      <c r="L164" t="inlineStr"/>
       <c r="M164" t="n">
         <v>0</v>
       </c>
@@ -12457,7 +12352,6 @@
       <c r="G170" t="n">
         <v>26</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>26*</t>
@@ -12601,7 +12495,6 @@
       <c r="G172" t="n">
         <v>23</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>23*</t>
@@ -12964,15 +12857,12 @@
       <c r="G177" t="n">
         <v>0</v>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
       </c>
-      <c r="L177" t="inlineStr"/>
       <c r="M177" t="n">
         <v>0</v>
       </c>
@@ -13248,15 +13138,12 @@
       <c r="G181" t="n">
         <v>0</v>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
         <v>0</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
       </c>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="n">
         <v>0</v>
       </c>
@@ -13678,7 +13565,6 @@
       <c r="G187" t="n">
         <v>9</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>9*</t>
@@ -13822,15 +13708,12 @@
       <c r="G189" t="n">
         <v>0</v>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
         <v>0</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
       </c>
-      <c r="L189" t="inlineStr"/>
       <c r="M189" t="n">
         <v>0</v>
       </c>
@@ -14033,15 +13916,12 @@
       <c r="G192" t="n">
         <v>0</v>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
         <v>0</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
       </c>
-      <c r="L192" t="inlineStr"/>
       <c r="M192" t="n">
         <v>0</v>
       </c>
@@ -14098,7 +13978,6 @@
       <c r="G193" t="n">
         <v>1</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>1*</t>
@@ -14534,7 +14413,6 @@
       <c r="G199" t="n">
         <v>1</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>1*</t>
@@ -14605,7 +14483,6 @@
       <c r="G200" t="n">
         <v>8</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>8*</t>
@@ -14749,15 +14626,12 @@
       <c r="G202" t="n">
         <v>0</v>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
       </c>
-      <c r="L202" t="inlineStr"/>
       <c r="M202" t="n">
         <v>0</v>
       </c>
@@ -14887,7 +14761,6 @@
       <c r="G204" t="n">
         <v>7</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>7*</t>
@@ -15396,15 +15269,12 @@
       <c r="G211" t="n">
         <v>0</v>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="n">
         <v>0</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
-      <c r="L211" t="inlineStr"/>
       <c r="M211" t="n">
         <v>0</v>
       </c>
@@ -15826,7 +15696,6 @@
       <c r="G217" t="n">
         <v>0</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>0*</t>
@@ -16262,7 +16131,6 @@
       <c r="G223" t="n">
         <v>2</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>2*</t>
@@ -16479,15 +16347,12 @@
       <c r="G226" t="n">
         <v>0</v>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="n">
         <v>0</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
       </c>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="n">
         <v>0</v>
       </c>
@@ -16617,15 +16482,12 @@
       <c r="G228" t="n">
         <v>0</v>
       </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="n">
         <v>0</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
       </c>
-      <c r="L228" t="inlineStr"/>
       <c r="M228" t="n">
         <v>0</v>
       </c>
@@ -16755,15 +16617,12 @@
       <c r="G230" t="n">
         <v>0</v>
       </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="n">
         <v>0</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
       </c>
-      <c r="L230" t="inlineStr"/>
       <c r="M230" t="n">
         <v>0</v>
       </c>
@@ -16966,15 +16825,12 @@
       <c r="G233" t="n">
         <v>0</v>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="n">
         <v>0</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
       </c>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="n">
         <v>0</v>
       </c>
@@ -17104,15 +16960,12 @@
       <c r="G235" t="n">
         <v>0</v>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="n">
         <v>0</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
       </c>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="n">
         <v>0</v>
       </c>
@@ -17315,7 +17168,6 @@
       <c r="G238" t="n">
         <v>45</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>45*</t>
@@ -17386,15 +17238,12 @@
       <c r="G239" t="n">
         <v>0</v>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
       </c>
-      <c r="L239" t="inlineStr"/>
       <c r="M239" t="n">
         <v>0</v>
       </c>
@@ -17451,7 +17300,6 @@
       <c r="G240" t="n">
         <v>152</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>152*</t>
@@ -17668,15 +17516,12 @@
       <c r="G243" t="n">
         <v>0</v>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="n">
         <v>0</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
       </c>
-      <c r="L243" t="inlineStr"/>
       <c r="M243" t="n">
         <v>0</v>
       </c>
@@ -17733,7 +17578,6 @@
       <c r="G244" t="n">
         <v>6</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>6*</t>
@@ -17950,7 +17794,6 @@
       <c r="G247" t="n">
         <v>82</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>82*</t>
@@ -18240,7 +18083,6 @@
       <c r="G251" t="n">
         <v>1</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>1*</t>
@@ -18895,7 +18737,6 @@
       <c r="G260" t="n">
         <v>2</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>2*</t>
@@ -18966,15 +18807,12 @@
       <c r="G261" t="n">
         <v>0</v>
       </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="n">
         <v>0</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
       </c>
-      <c r="L261" t="inlineStr"/>
       <c r="M261" t="n">
         <v>0</v>
       </c>
@@ -19323,15 +19161,12 @@
       <c r="G266" t="n">
         <v>0</v>
       </c>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="n">
         <v>0</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
       </c>
-      <c r="L266" t="inlineStr"/>
       <c r="M266" t="n">
         <v>0</v>
       </c>
@@ -19388,7 +19223,6 @@
       <c r="G267" t="n">
         <v>43</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>43*</t>
@@ -19459,15 +19293,12 @@
       <c r="G268" t="n">
         <v>0</v>
       </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="n">
         <v>0</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
       </c>
-      <c r="L268" t="inlineStr"/>
       <c r="M268" t="n">
         <v>0</v>
       </c>
@@ -19524,15 +19355,12 @@
       <c r="G269" t="n">
         <v>0</v>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="n">
         <v>0</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
       </c>
-      <c r="L269" t="inlineStr"/>
       <c r="M269" t="n">
         <v>0</v>
       </c>
@@ -19735,15 +19563,12 @@
       <c r="G272" t="n">
         <v>0</v>
       </c>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="n">
         <v>0</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
       </c>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
         <v>0</v>
       </c>
@@ -19873,15 +19698,12 @@
       <c r="G274" t="n">
         <v>0</v>
       </c>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="n">
         <v>0</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
       </c>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
         <v>0</v>
       </c>
@@ -19938,7 +19760,6 @@
       <c r="G275" t="n">
         <v>109</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>109*</t>
@@ -20009,15 +19830,12 @@
       <c r="G276" t="n">
         <v>0</v>
       </c>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="n">
         <v>0</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
         <v>0</v>
       </c>
@@ -20074,15 +19892,12 @@
       <c r="G277" t="n">
         <v>0</v>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="n">
         <v>0</v>
       </c>
       <c r="K277" t="n">
         <v>0</v>
       </c>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
         <v>0</v>
       </c>
@@ -20139,7 +19954,6 @@
       <c r="G278" t="n">
         <v>2</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>2*</t>
@@ -20210,15 +20024,12 @@
       <c r="G279" t="n">
         <v>0</v>
       </c>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="n">
         <v>0</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
       </c>
-      <c r="L279" t="inlineStr"/>
       <c r="M279" t="n">
         <v>0</v>
       </c>
@@ -20494,15 +20305,12 @@
       <c r="G283" t="n">
         <v>0</v>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="n">
         <v>0</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
       </c>
-      <c r="L283" t="inlineStr"/>
       <c r="M283" t="n">
         <v>0</v>
       </c>
@@ -20559,7 +20367,6 @@
       <c r="G284" t="n">
         <v>30</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>30*</t>
@@ -20703,15 +20510,12 @@
       <c r="G286" t="n">
         <v>0</v>
       </c>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="n">
         <v>0</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
       </c>
-      <c r="L286" t="inlineStr"/>
       <c r="M286" t="n">
         <v>0</v>
       </c>
@@ -20768,15 +20572,12 @@
       <c r="G287" t="n">
         <v>0</v>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="n">
         <v>0</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
       </c>
-      <c r="L287" t="inlineStr"/>
       <c r="M287" t="n">
         <v>0</v>
       </c>
@@ -20833,7 +20634,6 @@
       <c r="G288" t="n">
         <v>0</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>0*</t>
@@ -20904,15 +20704,12 @@
       <c r="G289" t="n">
         <v>0</v>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="n">
         <v>0</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
       </c>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="n">
         <v>0</v>
       </c>
@@ -21042,7 +20839,6 @@
       <c r="G291" t="n">
         <v>0</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>0*</t>
@@ -21054,7 +20850,6 @@
       <c r="K291" t="n">
         <v>0</v>
       </c>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="n">
         <v>0</v>
       </c>
@@ -21111,15 +20906,12 @@
       <c r="G292" t="n">
         <v>0</v>
       </c>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="n">
         <v>0</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
       </c>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="n">
         <v>0</v>
       </c>
@@ -21176,15 +20968,12 @@
       <c r="G293" t="n">
         <v>0</v>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="n">
         <v>0</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
       </c>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="n">
         <v>0</v>
       </c>
@@ -21241,15 +21030,12 @@
       <c r="G294" t="n">
         <v>0</v>
       </c>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="n">
         <v>0</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="n">
         <v>0</v>
       </c>
@@ -21306,15 +21092,12 @@
       <c r="G295" t="n">
         <v>0</v>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="n">
         <v>0</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
       </c>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="n">
         <v>0</v>
       </c>
@@ -21809,15 +21592,12 @@
       <c r="G302" t="n">
         <v>0</v>
       </c>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="n">
         <v>0</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
       </c>
-      <c r="L302" t="inlineStr"/>
       <c r="M302" t="n">
         <v>0</v>
       </c>
@@ -21874,15 +21654,12 @@
       <c r="G303" t="n">
         <v>0</v>
       </c>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="n">
         <v>0</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
       </c>
-      <c r="L303" t="inlineStr"/>
       <c r="M303" t="n">
         <v>0</v>
       </c>
@@ -22304,7 +22081,6 @@
       <c r="G309" t="n">
         <v>47</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>47*</t>
@@ -22448,15 +22224,12 @@
       <c r="G311" t="n">
         <v>0</v>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="n">
         <v>0</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
       </c>
-      <c r="L311" t="inlineStr"/>
       <c r="M311" t="n">
         <v>0</v>
       </c>
@@ -22586,15 +22359,12 @@
       <c r="G313" t="n">
         <v>0</v>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="n">
         <v>0</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
       </c>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="n">
         <v>0</v>
       </c>
@@ -22724,7 +22494,6 @@
       <c r="G315" t="n">
         <v>73</v>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>73*</t>
@@ -22868,15 +22637,12 @@
       <c r="G317" t="n">
         <v>0</v>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="n">
         <v>0</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
       </c>
-      <c r="L317" t="inlineStr"/>
       <c r="M317" t="n">
         <v>0</v>
       </c>
@@ -22933,15 +22699,12 @@
       <c r="G318" t="n">
         <v>0</v>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="n">
         <v>0</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
       </c>
-      <c r="L318" t="inlineStr"/>
       <c r="M318" t="n">
         <v>0</v>
       </c>
@@ -23144,15 +22907,12 @@
       <c r="G321" t="n">
         <v>0</v>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="n">
         <v>0</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
       </c>
-      <c r="L321" t="inlineStr"/>
       <c r="M321" t="n">
         <v>0</v>
       </c>
@@ -23209,7 +22969,6 @@
       <c r="G322" t="n">
         <v>20</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>20*</t>
@@ -23426,15 +23185,12 @@
       <c r="G325" t="n">
         <v>0</v>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="n">
         <v>0</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
       </c>
-      <c r="L325" t="inlineStr"/>
       <c r="M325" t="n">
         <v>0</v>
       </c>
@@ -23491,7 +23247,6 @@
       <c r="G326" t="n">
         <v>8</v>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>8*</t>
@@ -23635,15 +23390,12 @@
       <c r="G328" t="n">
         <v>0</v>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="n">
         <v>0</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
       </c>
-      <c r="L328" t="inlineStr"/>
       <c r="M328" t="n">
         <v>0</v>
       </c>
@@ -23773,15 +23525,12 @@
       <c r="G330" t="n">
         <v>0</v>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="n">
         <v>0</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
       </c>
-      <c r="L330" t="inlineStr"/>
       <c r="M330" t="n">
         <v>0</v>
       </c>
@@ -23838,7 +23587,6 @@
       <c r="G331" t="n">
         <v>43</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>43*</t>
@@ -23909,7 +23657,6 @@
       <c r="G332" t="n">
         <v>0</v>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>0*</t>
@@ -23921,7 +23668,6 @@
       <c r="K332" t="n">
         <v>0</v>
       </c>
-      <c r="L332" t="inlineStr"/>
       <c r="M332" t="n">
         <v>0</v>
       </c>
@@ -23978,15 +23724,12 @@
       <c r="G333" t="n">
         <v>0</v>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
       <c r="J333" t="n">
         <v>0</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
       </c>
-      <c r="L333" t="inlineStr"/>
       <c r="M333" t="n">
         <v>0</v>
       </c>
@@ -24043,15 +23786,12 @@
       <c r="G334" t="n">
         <v>0</v>
       </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
       <c r="J334" t="n">
         <v>0</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
       </c>
-      <c r="L334" t="inlineStr"/>
       <c r="M334" t="n">
         <v>0</v>
       </c>
@@ -24108,15 +23848,12 @@
       <c r="G335" t="n">
         <v>0</v>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
       <c r="J335" t="n">
         <v>0</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
       </c>
-      <c r="L335" t="inlineStr"/>
       <c r="M335" t="n">
         <v>0</v>
       </c>
@@ -24538,7 +24275,6 @@
       <c r="G341" t="n">
         <v>207</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>207*</t>
@@ -24609,15 +24345,12 @@
       <c r="G342" t="n">
         <v>0</v>
       </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
       <c r="J342" t="n">
         <v>0</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
       </c>
-      <c r="L342" t="inlineStr"/>
       <c r="M342" t="n">
         <v>0</v>
       </c>
@@ -24674,15 +24407,12 @@
       <c r="G343" t="n">
         <v>0</v>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
       <c r="J343" t="n">
         <v>0</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
       </c>
-      <c r="L343" t="inlineStr"/>
       <c r="M343" t="n">
         <v>0</v>
       </c>
@@ -24739,15 +24469,12 @@
       <c r="G344" t="n">
         <v>0</v>
       </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
       <c r="J344" t="n">
         <v>0</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
       </c>
-      <c r="L344" t="inlineStr"/>
       <c r="M344" t="n">
         <v>0</v>
       </c>
@@ -24804,15 +24531,12 @@
       <c r="G345" t="n">
         <v>0</v>
       </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
       <c r="J345" t="n">
         <v>0</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
       </c>
-      <c r="L345" t="inlineStr"/>
       <c r="M345" t="n">
         <v>0</v>
       </c>
@@ -25161,7 +24885,6 @@
       <c r="G350" t="n">
         <v>7</v>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>7*</t>
@@ -25305,15 +25028,12 @@
       <c r="G352" t="n">
         <v>0</v>
       </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
       <c r="J352" t="n">
         <v>0</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
       </c>
-      <c r="L352" t="inlineStr"/>
       <c r="M352" t="n">
         <v>0</v>
       </c>
@@ -25662,15 +25382,12 @@
       <c r="G357" t="n">
         <v>0</v>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="n">
         <v>0</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
       </c>
-      <c r="L357" t="inlineStr"/>
       <c r="M357" t="n">
         <v>0</v>
       </c>
@@ -25800,15 +25517,12 @@
       <c r="G359" t="n">
         <v>0</v>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
       <c r="J359" t="n">
         <v>0</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
-      <c r="L359" t="inlineStr"/>
       <c r="M359" t="n">
         <v>0</v>
       </c>
@@ -26157,7 +25871,6 @@
       <c r="G364" t="n">
         <v>77</v>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>77*</t>
@@ -26666,7 +26379,6 @@
       <c r="G371" t="n">
         <v>25</v>
       </c>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr">
         <is>
           <t>25*</t>
@@ -26737,15 +26449,12 @@
       <c r="G372" t="n">
         <v>0</v>
       </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
       <c r="J372" t="n">
         <v>0</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
       </c>
-      <c r="L372" t="inlineStr"/>
       <c r="M372" t="n">
         <v>0</v>
       </c>
@@ -26875,7 +26584,6 @@
       <c r="G374" t="n">
         <v>0</v>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr">
         <is>
           <t>0*</t>
@@ -27384,15 +27092,12 @@
       <c r="G381" t="n">
         <v>0</v>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="n">
         <v>0</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
       </c>
-      <c r="L381" t="inlineStr"/>
       <c r="M381" t="n">
         <v>0</v>
       </c>
@@ -27595,7 +27300,6 @@
       <c r="G384" t="n">
         <v>157</v>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>157*</t>
@@ -27739,15 +27443,12 @@
       <c r="G386" t="n">
         <v>0</v>
       </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
       <c r="J386" t="n">
         <v>0</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
       </c>
-      <c r="L386" t="inlineStr"/>
       <c r="M386" t="n">
         <v>0</v>
       </c>
@@ -28096,15 +27797,12 @@
       <c r="G391" t="n">
         <v>0</v>
       </c>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
       <c r="J391" t="n">
         <v>0</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
       </c>
-      <c r="L391" t="inlineStr"/>
       <c r="M391" t="n">
         <v>0</v>
       </c>
@@ -28307,15 +28005,12 @@
       <c r="G394" t="n">
         <v>0</v>
       </c>
-      <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
       <c r="J394" t="n">
         <v>0</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
       </c>
-      <c r="L394" t="inlineStr"/>
       <c r="M394" t="n">
         <v>0</v>
       </c>
@@ -28372,7 +28067,6 @@
       <c r="G395" t="n">
         <v>8</v>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>8*</t>
@@ -28443,7 +28137,6 @@
       <c r="G396" t="n">
         <v>19</v>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>19*</t>
@@ -28733,7 +28426,6 @@
       <c r="G400" t="n">
         <v>18</v>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>18*</t>
@@ -28877,7 +28569,6 @@
       <c r="G402" t="n">
         <v>49</v>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>49*</t>
@@ -29021,7 +28712,6 @@
       <c r="G404" t="n">
         <v>0</v>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>0*</t>
@@ -29033,7 +28723,6 @@
       <c r="K404" t="n">
         <v>0</v>
       </c>
-      <c r="L404" t="inlineStr"/>
       <c r="M404" t="n">
         <v>0</v>
       </c>
@@ -29528,7 +29217,6 @@
       <c r="G411" t="n">
         <v>2</v>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>2*</t>
@@ -30183,15 +29871,12 @@
       <c r="G420" t="n">
         <v>0</v>
       </c>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
       <c r="J420" t="n">
         <v>0</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
       </c>
-      <c r="L420" t="inlineStr"/>
       <c r="M420" t="n">
         <v>0</v>
       </c>
@@ -30248,15 +29933,12 @@
       <c r="G421" t="n">
         <v>0</v>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="n">
         <v>0</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
       </c>
-      <c r="L421" t="inlineStr"/>
       <c r="M421" t="n">
         <v>0</v>
       </c>
@@ -30605,7 +30287,6 @@
       <c r="G426" t="n">
         <v>8</v>
       </c>
-      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>8*</t>
@@ -30749,7 +30430,6 @@
       <c r="G428" t="n">
         <v>18</v>
       </c>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
           <t>18*</t>
@@ -31039,15 +30719,12 @@
       <c r="G432" t="n">
         <v>0</v>
       </c>
-      <c r="H432" t="inlineStr"/>
-      <c r="I432" t="inlineStr"/>
       <c r="J432" t="n">
         <v>0</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
       </c>
-      <c r="L432" t="inlineStr"/>
       <c r="M432" t="n">
         <v>0</v>
       </c>
@@ -31323,15 +31000,12 @@
       <c r="G436" t="n">
         <v>0</v>
       </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
       <c r="J436" t="n">
         <v>0</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
       </c>
-      <c r="L436" t="inlineStr"/>
       <c r="M436" t="n">
         <v>0</v>
       </c>
@@ -31534,7 +31208,6 @@
       <c r="G439" t="n">
         <v>104</v>
       </c>
-      <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr">
         <is>
           <t>104*</t>
@@ -31678,15 +31351,12 @@
       <c r="G441" t="n">
         <v>0</v>
       </c>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
       <c r="J441" t="n">
         <v>0</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
       </c>
-      <c r="L441" t="inlineStr"/>
       <c r="M441" t="n">
         <v>0</v>
       </c>
@@ -31743,7 +31413,6 @@
       <c r="G442" t="n">
         <v>4</v>
       </c>
-      <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr">
         <is>
           <t>4*</t>
@@ -32398,15 +32067,12 @@
       <c r="G451" t="n">
         <v>0</v>
       </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
       <c r="J451" t="n">
         <v>0</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
       </c>
-      <c r="L451" t="inlineStr"/>
       <c r="M451" t="n">
         <v>0</v>
       </c>
@@ -32974,15 +32640,12 @@
       <c r="G459" t="n">
         <v>0</v>
       </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
       <c r="J459" t="n">
         <v>0</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
       </c>
-      <c r="L459" t="inlineStr"/>
       <c r="M459" t="n">
         <v>0</v>
       </c>
@@ -33185,7 +32848,6 @@
       <c r="G462" t="n">
         <v>0</v>
       </c>
-      <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr">
         <is>
           <t>0*</t>
@@ -33256,7 +32918,6 @@
       <c r="G463" t="n">
         <v>14</v>
       </c>
-      <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr">
         <is>
           <t>14*</t>
@@ -33400,15 +33061,12 @@
       <c r="G465" t="n">
         <v>0</v>
       </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
       <c r="J465" t="n">
         <v>0</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
       </c>
-      <c r="L465" t="inlineStr"/>
       <c r="M465" t="n">
         <v>0</v>
       </c>
@@ -33465,7 +33123,6 @@
       <c r="G466" t="n">
         <v>120</v>
       </c>
-      <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr">
         <is>
           <t>120*</t>
@@ -33536,7 +33193,6 @@
       <c r="G467" t="n">
         <v>9</v>
       </c>
-      <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr">
         <is>
           <t>9*</t>
@@ -33899,15 +33555,12 @@
       <c r="G472" t="n">
         <v>0</v>
       </c>
-      <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr"/>
       <c r="J472" t="n">
         <v>0</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
       </c>
-      <c r="L472" t="inlineStr"/>
       <c r="M472" t="n">
         <v>0</v>
       </c>
@@ -34037,15 +33690,12 @@
       <c r="G474" t="n">
         <v>0</v>
       </c>
-      <c r="H474" t="inlineStr"/>
-      <c r="I474" t="inlineStr"/>
       <c r="J474" t="n">
         <v>0</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
       </c>
-      <c r="L474" t="inlineStr"/>
       <c r="M474" t="n">
         <v>0</v>
       </c>
@@ -34248,15 +33898,12 @@
       <c r="G477" t="n">
         <v>0</v>
       </c>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
       <c r="J477" t="n">
         <v>0</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
       </c>
-      <c r="L477" t="inlineStr"/>
       <c r="M477" t="n">
         <v>0</v>
       </c>
@@ -34605,15 +34252,12 @@
       <c r="G482" t="n">
         <v>0</v>
       </c>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
       <c r="J482" t="n">
         <v>0</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
       </c>
-      <c r="L482" t="inlineStr"/>
       <c r="M482" t="n">
         <v>0</v>
       </c>
@@ -34670,7 +34314,6 @@
       <c r="G483" t="n">
         <v>62</v>
       </c>
-      <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr">
         <is>
           <t>62*</t>
@@ -34741,15 +34384,12 @@
       <c r="G484" t="n">
         <v>0</v>
       </c>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
       <c r="J484" t="n">
         <v>0</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
       </c>
-      <c r="L484" t="inlineStr"/>
       <c r="M484" t="n">
         <v>0</v>
       </c>
@@ -35025,7 +34665,6 @@
       <c r="G488" t="n">
         <v>25</v>
       </c>
-      <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr">
         <is>
           <t>25*</t>
@@ -35315,7 +34954,6 @@
       <c r="G492" t="n">
         <v>30</v>
       </c>
-      <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr">
         <is>
           <t>30*</t>
@@ -35459,15 +35097,12 @@
       <c r="G494" t="n">
         <v>0</v>
       </c>
-      <c r="H494" t="inlineStr"/>
-      <c r="I494" t="inlineStr"/>
       <c r="J494" t="n">
         <v>0</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
       </c>
-      <c r="L494" t="inlineStr"/>
       <c r="M494" t="n">
         <v>0</v>
       </c>
@@ -35816,15 +35451,12 @@
       <c r="G499" t="n">
         <v>0</v>
       </c>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
       <c r="J499" t="n">
         <v>0</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
       </c>
-      <c r="L499" t="inlineStr"/>
       <c r="M499" t="n">
         <v>0</v>
       </c>
@@ -35881,15 +35513,12 @@
       <c r="G500" t="n">
         <v>0</v>
       </c>
-      <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
       <c r="J500" t="n">
         <v>0</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
       </c>
-      <c r="L500" t="inlineStr"/>
       <c r="M500" t="n">
         <v>0</v>
       </c>
@@ -36019,7 +35648,6 @@
       <c r="G502" t="n">
         <v>14</v>
       </c>
-      <c r="H502" t="inlineStr"/>
       <c r="I502" t="inlineStr">
         <is>
           <t>14*</t>
@@ -36163,15 +35791,12 @@
       <c r="G504" t="n">
         <v>0</v>
       </c>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
       <c r="J504" t="n">
         <v>0</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
       </c>
-      <c r="L504" t="inlineStr"/>
       <c r="M504" t="n">
         <v>0</v>
       </c>
@@ -36228,7 +35853,6 @@
       <c r="G505" t="n">
         <v>38</v>
       </c>
-      <c r="H505" t="inlineStr"/>
       <c r="I505" t="inlineStr">
         <is>
           <t>38*</t>
@@ -36518,15 +36142,12 @@
       <c r="G509" t="n">
         <v>0</v>
       </c>
-      <c r="H509" t="inlineStr"/>
-      <c r="I509" t="inlineStr"/>
       <c r="J509" t="n">
         <v>0</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
       </c>
-      <c r="L509" t="inlineStr"/>
       <c r="M509" t="n">
         <v>0</v>
       </c>
@@ -36583,7 +36204,6 @@
       <c r="G510" t="n">
         <v>2</v>
       </c>
-      <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr">
         <is>
           <t>2*</t>
@@ -36800,15 +36420,12 @@
       <c r="G513" t="n">
         <v>0</v>
       </c>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
       <c r="J513" t="n">
         <v>0</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
       </c>
-      <c r="L513" t="inlineStr"/>
       <c r="M513" t="n">
         <v>0</v>
       </c>
@@ -37376,7 +36993,6 @@
       <c r="G521" t="n">
         <v>51</v>
       </c>
-      <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr">
         <is>
           <t>51*</t>
@@ -37520,15 +37136,12 @@
       <c r="G523" t="n">
         <v>0</v>
       </c>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr"/>
       <c r="J523" t="n">
         <v>0</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
       </c>
-      <c r="L523" t="inlineStr"/>
       <c r="M523" t="n">
         <v>0</v>
       </c>
@@ -37585,15 +37198,12 @@
       <c r="G524" t="n">
         <v>0</v>
       </c>
-      <c r="H524" t="inlineStr"/>
-      <c r="I524" t="inlineStr"/>
       <c r="J524" t="n">
         <v>0</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
       </c>
-      <c r="L524" t="inlineStr"/>
       <c r="M524" t="n">
         <v>0</v>
       </c>
@@ -37723,15 +37333,12 @@
       <c r="G526" t="n">
         <v>0</v>
       </c>
-      <c r="H526" t="inlineStr"/>
-      <c r="I526" t="inlineStr"/>
       <c r="J526" t="n">
         <v>0</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
       </c>
-      <c r="L526" t="inlineStr"/>
       <c r="M526" t="n">
         <v>0</v>
       </c>
@@ -37861,7 +37468,6 @@
       <c r="G528" t="n">
         <v>1</v>
       </c>
-      <c r="H528" t="inlineStr"/>
       <c r="I528" t="inlineStr">
         <is>
           <t>1*</t>
@@ -38005,15 +37611,12 @@
       <c r="G530" t="n">
         <v>0</v>
       </c>
-      <c r="H530" t="inlineStr"/>
-      <c r="I530" t="inlineStr"/>
       <c r="J530" t="n">
         <v>0</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
       </c>
-      <c r="L530" t="inlineStr"/>
       <c r="M530" t="n">
         <v>0</v>
       </c>
@@ -38508,15 +38111,12 @@
       <c r="G537" t="n">
         <v>0</v>
       </c>
-      <c r="H537" t="inlineStr"/>
-      <c r="I537" t="inlineStr"/>
       <c r="J537" t="n">
         <v>0</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
       </c>
-      <c r="L537" t="inlineStr"/>
       <c r="M537" t="n">
         <v>0</v>
       </c>
@@ -38865,7 +38465,6 @@
       <c r="G542" t="n">
         <v>14</v>
       </c>
-      <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr">
         <is>
           <t>14*</t>
@@ -39009,7 +38608,6 @@
       <c r="G544" t="n">
         <v>3</v>
       </c>
-      <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr">
         <is>
           <t>3*</t>
@@ -40029,7 +39627,6 @@
       <c r="G558" t="n">
         <v>60</v>
       </c>
-      <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr">
         <is>
           <t>60*</t>
@@ -40246,7 +39843,6 @@
       <c r="G561" t="n">
         <v>17</v>
       </c>
-      <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr">
         <is>
           <t>17*</t>
@@ -40317,7 +39913,6 @@
       <c r="G562" t="n">
         <v>17</v>
       </c>
-      <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr">
         <is>
           <t>17*</t>
@@ -41337,7 +40932,6 @@
       <c r="G576" t="n">
         <v>11</v>
       </c>
-      <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr">
         <is>
           <t>11*</t>
@@ -41627,15 +41221,12 @@
       <c r="G580" t="n">
         <v>0</v>
       </c>
-      <c r="H580" t="inlineStr"/>
-      <c r="I580" t="inlineStr"/>
       <c r="J580" t="n">
         <v>0</v>
       </c>
       <c r="K580" t="n">
         <v>0</v>
       </c>
-      <c r="L580" t="inlineStr"/>
       <c r="M580" t="n">
         <v>0</v>
       </c>
@@ -41838,15 +41429,12 @@
       <c r="G583" t="n">
         <v>0</v>
       </c>
-      <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr"/>
       <c r="J583" t="n">
         <v>0</v>
       </c>
       <c r="K583" t="n">
         <v>0</v>
       </c>
-      <c r="L583" t="inlineStr"/>
       <c r="M583" t="n">
         <v>0</v>
       </c>
@@ -41903,7 +41491,6 @@
       <c r="G584" t="n">
         <v>22</v>
       </c>
-      <c r="H584" t="inlineStr"/>
       <c r="I584" t="inlineStr">
         <is>
           <t>22*</t>
@@ -42266,7 +41853,6 @@
       <c r="G589" t="n">
         <v>38</v>
       </c>
-      <c r="H589" t="inlineStr"/>
       <c r="I589" t="inlineStr">
         <is>
           <t>38*</t>
@@ -42337,15 +41923,12 @@
       <c r="G590" t="n">
         <v>0</v>
       </c>
-      <c r="H590" t="inlineStr"/>
-      <c r="I590" t="inlineStr"/>
       <c r="J590" t="n">
         <v>0</v>
       </c>
       <c r="K590" t="n">
         <v>0</v>
       </c>
-      <c r="L590" t="inlineStr"/>
       <c r="M590" t="n">
         <v>0</v>
       </c>
@@ -42402,15 +41985,12 @@
       <c r="G591" t="n">
         <v>0</v>
       </c>
-      <c r="H591" t="inlineStr"/>
-      <c r="I591" t="inlineStr"/>
       <c r="J591" t="n">
         <v>0</v>
       </c>
       <c r="K591" t="n">
         <v>0</v>
       </c>
-      <c r="L591" t="inlineStr"/>
       <c r="M591" t="n">
         <v>0</v>
       </c>
@@ -42686,7 +42266,6 @@
       <c r="G595" t="n">
         <v>61</v>
       </c>
-      <c r="H595" t="inlineStr"/>
       <c r="I595" t="inlineStr">
         <is>
           <t>61*</t>
@@ -43560,7 +43139,6 @@
       <c r="G607" t="n">
         <v>0</v>
       </c>
-      <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr">
         <is>
           <t>0*</t>
@@ -43572,7 +43150,6 @@
       <c r="K607" t="n">
         <v>0</v>
       </c>
-      <c r="L607" t="inlineStr"/>
       <c r="M607" t="n">
         <v>0</v>
       </c>
@@ -43702,7 +43279,6 @@
       <c r="G609" t="n">
         <v>9</v>
       </c>
-      <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr">
         <is>
           <t>9*</t>
@@ -44065,15 +43641,12 @@
       <c r="G614" t="n">
         <v>0</v>
       </c>
-      <c r="H614" t="inlineStr"/>
-      <c r="I614" t="inlineStr"/>
       <c r="J614" t="n">
         <v>0</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
       </c>
-      <c r="L614" t="inlineStr"/>
       <c r="M614" t="n">
         <v>0</v>
       </c>
@@ -44203,15 +43776,12 @@
       <c r="G616" t="n">
         <v>0</v>
       </c>
-      <c r="H616" t="inlineStr"/>
-      <c r="I616" t="inlineStr"/>
       <c r="J616" t="n">
         <v>0</v>
       </c>
       <c r="K616" t="n">
         <v>0</v>
       </c>
-      <c r="L616" t="inlineStr"/>
       <c r="M616" t="n">
         <v>0</v>
       </c>
@@ -44414,15 +43984,12 @@
       <c r="G619" t="n">
         <v>0</v>
       </c>
-      <c r="H619" t="inlineStr"/>
-      <c r="I619" t="inlineStr"/>
       <c r="J619" t="n">
         <v>0</v>
       </c>
       <c r="K619" t="n">
         <v>0</v>
       </c>
-      <c r="L619" t="inlineStr"/>
       <c r="M619" t="n">
         <v>0</v>
       </c>
@@ -44479,7 +44046,6 @@
       <c r="G620" t="n">
         <v>1</v>
       </c>
-      <c r="H620" t="inlineStr"/>
       <c r="I620" t="inlineStr">
         <is>
           <t>1*</t>
@@ -44988,15 +44554,12 @@
       <c r="G627" t="n">
         <v>0</v>
       </c>
-      <c r="H627" t="inlineStr"/>
-      <c r="I627" t="inlineStr"/>
       <c r="J627" t="n">
         <v>0</v>
       </c>
       <c r="K627" t="n">
         <v>0</v>
       </c>
-      <c r="L627" t="inlineStr"/>
       <c r="M627" t="n">
         <v>0</v>
       </c>
@@ -45126,15 +44689,12 @@
       <c r="G629" t="n">
         <v>0</v>
       </c>
-      <c r="H629" t="inlineStr"/>
-      <c r="I629" t="inlineStr"/>
       <c r="J629" t="n">
         <v>0</v>
       </c>
       <c r="K629" t="n">
         <v>0</v>
       </c>
-      <c r="L629" t="inlineStr"/>
       <c r="M629" t="n">
         <v>0</v>
       </c>
@@ -45264,15 +44824,12 @@
       <c r="G631" t="n">
         <v>0</v>
       </c>
-      <c r="H631" t="inlineStr"/>
-      <c r="I631" t="inlineStr"/>
       <c r="J631" t="n">
         <v>0</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
       </c>
-      <c r="L631" t="inlineStr"/>
       <c r="M631" t="n">
         <v>0</v>
       </c>
@@ -45329,15 +44886,12 @@
       <c r="G632" t="n">
         <v>0</v>
       </c>
-      <c r="H632" t="inlineStr"/>
-      <c r="I632" t="inlineStr"/>
       <c r="J632" t="n">
         <v>0</v>
       </c>
       <c r="K632" t="n">
         <v>0</v>
       </c>
-      <c r="L632" t="inlineStr"/>
       <c r="M632" t="n">
         <v>0</v>
       </c>
@@ -45394,15 +44948,12 @@
       <c r="G633" t="n">
         <v>0</v>
       </c>
-      <c r="H633" t="inlineStr"/>
-      <c r="I633" t="inlineStr"/>
       <c r="J633" t="n">
         <v>0</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
       </c>
-      <c r="L633" t="inlineStr"/>
       <c r="M633" t="n">
         <v>0</v>
       </c>
@@ -45459,15 +45010,12 @@
       <c r="G634" t="n">
         <v>0</v>
       </c>
-      <c r="H634" t="inlineStr"/>
-      <c r="I634" t="inlineStr"/>
       <c r="J634" t="n">
         <v>0</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
       </c>
-      <c r="L634" t="inlineStr"/>
       <c r="M634" t="n">
         <v>0</v>
       </c>
@@ -45743,7 +45291,6 @@
       <c r="G638" t="n">
         <v>2</v>
       </c>
-      <c r="H638" t="inlineStr"/>
       <c r="I638" t="inlineStr">
         <is>
           <t>2*</t>
@@ -46106,7 +45653,6 @@
       <c r="G643" t="n">
         <v>21</v>
       </c>
-      <c r="H643" t="inlineStr"/>
       <c r="I643" t="inlineStr">
         <is>
           <t>21*</t>
@@ -46615,7 +46161,6 @@
       <c r="G650" t="n">
         <v>64</v>
       </c>
-      <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr">
         <is>
           <t>64*</t>
@@ -46759,15 +46304,12 @@
       <c r="G652" t="n">
         <v>0</v>
       </c>
-      <c r="H652" t="inlineStr"/>
-      <c r="I652" t="inlineStr"/>
       <c r="J652" t="n">
         <v>0</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
       </c>
-      <c r="L652" t="inlineStr"/>
       <c r="M652" t="n">
         <v>0</v>
       </c>
@@ -46897,15 +46439,12 @@
       <c r="G654" t="n">
         <v>0</v>
       </c>
-      <c r="H654" t="inlineStr"/>
-      <c r="I654" t="inlineStr"/>
       <c r="J654" t="n">
         <v>0</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
       </c>
-      <c r="L654" t="inlineStr"/>
       <c r="M654" t="n">
         <v>0</v>
       </c>
@@ -47035,7 +46574,6 @@
       <c r="G656" t="n">
         <v>24</v>
       </c>
-      <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr">
         <is>
           <t>24*</t>
@@ -47471,7 +47009,6 @@
       <c r="G662" t="n">
         <v>10</v>
       </c>
-      <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr">
         <is>
           <t>10*</t>
@@ -47761,7 +47298,6 @@
       <c r="G666" t="n">
         <v>1</v>
       </c>
-      <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr">
         <is>
           <t>1*</t>
@@ -48927,7 +48463,6 @@
       <c r="G682" t="n">
         <v>68</v>
       </c>
-      <c r="H682" t="inlineStr"/>
       <c r="I682" t="inlineStr">
         <is>
           <t>68*</t>
@@ -49071,15 +48606,12 @@
       <c r="G684" t="n">
         <v>0</v>
       </c>
-      <c r="H684" t="inlineStr"/>
-      <c r="I684" t="inlineStr"/>
       <c r="J684" t="n">
         <v>0</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
       </c>
-      <c r="L684" t="inlineStr"/>
       <c r="M684" t="n">
         <v>0</v>
       </c>
@@ -49574,15 +49106,12 @@
       <c r="G691" t="n">
         <v>0</v>
       </c>
-      <c r="H691" t="inlineStr"/>
-      <c r="I691" t="inlineStr"/>
       <c r="J691" t="n">
         <v>0</v>
       </c>
       <c r="K691" t="n">
         <v>0</v>
       </c>
-      <c r="L691" t="inlineStr"/>
       <c r="M691" t="n">
         <v>0</v>
       </c>
@@ -49639,15 +49168,12 @@
       <c r="G692" t="n">
         <v>0</v>
       </c>
-      <c r="H692" t="inlineStr"/>
-      <c r="I692" t="inlineStr"/>
       <c r="J692" t="n">
         <v>0</v>
       </c>
       <c r="K692" t="n">
         <v>0</v>
       </c>
-      <c r="L692" t="inlineStr"/>
       <c r="M692" t="n">
         <v>0</v>
       </c>
@@ -49704,7 +49230,6 @@
       <c r="G693" t="n">
         <v>40</v>
       </c>
-      <c r="H693" t="inlineStr"/>
       <c r="I693" t="inlineStr">
         <is>
           <t>40*</t>
@@ -49848,15 +49373,12 @@
       <c r="G695" t="n">
         <v>0</v>
       </c>
-      <c r="H695" t="inlineStr"/>
-      <c r="I695" t="inlineStr"/>
       <c r="J695" t="n">
         <v>0</v>
       </c>
       <c r="K695" t="n">
         <v>0</v>
       </c>
-      <c r="L695" t="inlineStr"/>
       <c r="M695" t="n">
         <v>0</v>
       </c>
@@ -50132,7 +49654,6 @@
       <c r="G699" t="n">
         <v>9</v>
       </c>
-      <c r="H699" t="inlineStr"/>
       <c r="I699" t="inlineStr">
         <is>
           <t>9*</t>
@@ -50203,15 +49724,12 @@
       <c r="G700" t="n">
         <v>0</v>
       </c>
-      <c r="H700" t="inlineStr"/>
-      <c r="I700" t="inlineStr"/>
       <c r="J700" t="n">
         <v>0</v>
       </c>
       <c r="K700" t="n">
         <v>0</v>
       </c>
-      <c r="L700" t="inlineStr"/>
       <c r="M700" t="n">
         <v>0</v>
       </c>
@@ -50268,15 +49786,12 @@
       <c r="G701" t="n">
         <v>0</v>
       </c>
-      <c r="H701" t="inlineStr"/>
-      <c r="I701" t="inlineStr"/>
       <c r="J701" t="n">
         <v>0</v>
       </c>
       <c r="K701" t="n">
         <v>0</v>
       </c>
-      <c r="L701" t="inlineStr"/>
       <c r="M701" t="n">
         <v>0</v>
       </c>
@@ -50333,7 +49848,6 @@
       <c r="G702" t="n">
         <v>10</v>
       </c>
-      <c r="H702" t="inlineStr"/>
       <c r="I702" t="inlineStr">
         <is>
           <t>10*</t>
@@ -50477,15 +49991,12 @@
       <c r="G704" t="n">
         <v>0</v>
       </c>
-      <c r="H704" t="inlineStr"/>
-      <c r="I704" t="inlineStr"/>
       <c r="J704" t="n">
         <v>0</v>
       </c>
       <c r="K704" t="n">
         <v>0</v>
       </c>
-      <c r="L704" t="inlineStr"/>
       <c r="M704" t="n">
         <v>0</v>
       </c>
@@ -50761,7 +50272,6 @@
       <c r="G708" t="n">
         <v>4</v>
       </c>
-      <c r="H708" t="inlineStr"/>
       <c r="I708" t="inlineStr">
         <is>
           <t>4*</t>
@@ -50978,15 +50488,12 @@
       <c r="G711" t="n">
         <v>0</v>
       </c>
-      <c r="H711" t="inlineStr"/>
-      <c r="I711" t="inlineStr"/>
       <c r="J711" t="n">
         <v>0</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
       </c>
-      <c r="L711" t="inlineStr"/>
       <c r="M711" t="n">
         <v>0</v>
       </c>
@@ -51189,7 +50696,6 @@
       <c r="G714" t="n">
         <v>1</v>
       </c>
-      <c r="H714" t="inlineStr"/>
       <c r="I714" t="inlineStr">
         <is>
           <t>1*</t>
@@ -51698,15 +51204,12 @@
       <c r="G721" t="n">
         <v>0</v>
       </c>
-      <c r="H721" t="inlineStr"/>
-      <c r="I721" t="inlineStr"/>
       <c r="J721" t="n">
         <v>0</v>
       </c>
       <c r="K721" t="n">
         <v>0</v>
       </c>
-      <c r="L721" t="inlineStr"/>
       <c r="M721" t="n">
         <v>0</v>
       </c>
@@ -51836,7 +51339,6 @@
       <c r="G723" t="n">
         <v>37</v>
       </c>
-      <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr">
         <is>
           <t>37*</t>
@@ -52564,7 +52066,6 @@
       <c r="G733" t="n">
         <v>26</v>
       </c>
-      <c r="H733" t="inlineStr"/>
       <c r="I733" t="inlineStr">
         <is>
           <t>26*</t>
@@ -53511,7 +53012,6 @@
       <c r="G746" t="n">
         <v>0</v>
       </c>
-      <c r="H746" t="inlineStr"/>
       <c r="I746" t="inlineStr">
         <is>
           <t>0*</t>
@@ -53801,7 +53301,6 @@
       <c r="G750" t="n">
         <v>4</v>
       </c>
-      <c r="H750" t="inlineStr"/>
       <c r="I750" t="inlineStr">
         <is>
           <t>4*</t>
@@ -54018,15 +53517,12 @@
       <c r="G753" t="n">
         <v>0</v>
       </c>
-      <c r="H753" t="inlineStr"/>
-      <c r="I753" t="inlineStr"/>
       <c r="J753" t="n">
         <v>0</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
       </c>
-      <c r="L753" t="inlineStr"/>
       <c r="M753" t="n">
         <v>0</v>
       </c>
@@ -55105,7 +54601,6 @@
       <c r="G768" t="n">
         <v>4</v>
       </c>
-      <c r="H768" t="inlineStr"/>
       <c r="I768" t="inlineStr">
         <is>
           <t>4*</t>
@@ -55468,7 +54963,6 @@
       <c r="G773" t="n">
         <v>0</v>
       </c>
-      <c r="H773" t="inlineStr"/>
       <c r="I773" t="inlineStr">
         <is>
           <t>0*</t>
@@ -56050,7 +55544,6 @@
       <c r="G781" t="n">
         <v>0</v>
       </c>
-      <c r="H781" t="inlineStr"/>
       <c r="I781" t="inlineStr">
         <is>
           <t>0*</t>
@@ -56194,15 +55687,12 @@
       <c r="G783" t="n">
         <v>0</v>
       </c>
-      <c r="H783" t="inlineStr"/>
-      <c r="I783" t="inlineStr"/>
       <c r="J783" t="n">
         <v>0</v>
       </c>
       <c r="K783" t="n">
         <v>0</v>
       </c>
-      <c r="L783" t="inlineStr"/>
       <c r="M783" t="n">
         <v>0</v>
       </c>
@@ -56332,7 +55822,6 @@
       <c r="G785" t="n">
         <v>1</v>
       </c>
-      <c r="H785" t="inlineStr"/>
       <c r="I785" t="inlineStr">
         <is>
           <t>1*</t>
@@ -57060,15 +56549,12 @@
       <c r="G795" t="n">
         <v>0</v>
       </c>
-      <c r="H795" t="inlineStr"/>
-      <c r="I795" t="inlineStr"/>
       <c r="J795" t="n">
         <v>0</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
       </c>
-      <c r="L795" t="inlineStr"/>
       <c r="M795" t="n">
         <v>0</v>
       </c>
@@ -57344,7 +56830,6 @@
       <c r="G799" t="n">
         <v>13</v>
       </c>
-      <c r="H799" t="inlineStr"/>
       <c r="I799" t="inlineStr">
         <is>
           <t>13*</t>
@@ -57415,15 +56900,12 @@
       <c r="G800" t="n">
         <v>0</v>
       </c>
-      <c r="H800" t="inlineStr"/>
-      <c r="I800" t="inlineStr"/>
       <c r="J800" t="n">
         <v>0</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
       </c>
-      <c r="L800" t="inlineStr"/>
       <c r="M800" t="n">
         <v>0</v>
       </c>
@@ -57772,7 +57254,6 @@
       <c r="G805" t="n">
         <v>1</v>
       </c>
-      <c r="H805" t="inlineStr"/>
       <c r="I805" t="inlineStr">
         <is>
           <t>1*</t>
@@ -57843,7 +57324,6 @@
       <c r="G806" t="n">
         <v>0</v>
       </c>
-      <c r="H806" t="inlineStr"/>
       <c r="I806" t="inlineStr">
         <is>
           <t>0*</t>
@@ -57855,7 +57335,6 @@
       <c r="K806" t="n">
         <v>0</v>
       </c>
-      <c r="L806" t="inlineStr"/>
       <c r="M806" t="n">
         <v>0</v>
       </c>
@@ -58058,15 +57537,12 @@
       <c r="G809" t="n">
         <v>0</v>
       </c>
-      <c r="H809" t="inlineStr"/>
-      <c r="I809" t="inlineStr"/>
       <c r="J809" t="n">
         <v>0</v>
       </c>
       <c r="K809" t="n">
         <v>0</v>
       </c>
-      <c r="L809" t="inlineStr"/>
       <c r="M809" t="n">
         <v>0</v>
       </c>
@@ -58123,7 +57599,6 @@
       <c r="G810" t="n">
         <v>126</v>
       </c>
-      <c r="H810" t="inlineStr"/>
       <c r="I810" t="inlineStr">
         <is>
           <t>126*</t>
@@ -58413,15 +57888,12 @@
       <c r="G814" t="n">
         <v>0</v>
       </c>
-      <c r="H814" t="inlineStr"/>
-      <c r="I814" t="inlineStr"/>
       <c r="J814" t="n">
         <v>0</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
       </c>
-      <c r="L814" t="inlineStr"/>
       <c r="M814" t="n">
         <v>0</v>
       </c>
@@ -58478,15 +57950,12 @@
       <c r="G815" t="n">
         <v>0</v>
       </c>
-      <c r="H815" t="inlineStr"/>
-      <c r="I815" t="inlineStr"/>
       <c r="J815" t="n">
         <v>0</v>
       </c>
       <c r="K815" t="n">
         <v>0</v>
       </c>
-      <c r="L815" t="inlineStr"/>
       <c r="M815" t="n">
         <v>0</v>
       </c>
@@ -59127,7 +58596,6 @@
       <c r="G824" t="n">
         <v>13</v>
       </c>
-      <c r="H824" t="inlineStr"/>
       <c r="I824" t="inlineStr">
         <is>
           <t>13*</t>
@@ -59344,7 +58812,6 @@
       <c r="G827" t="n">
         <v>6</v>
       </c>
-      <c r="H827" t="inlineStr"/>
       <c r="I827" t="inlineStr">
         <is>
           <t>6*</t>
@@ -60948,15 +60415,12 @@
       <c r="G849" t="n">
         <v>0</v>
       </c>
-      <c r="H849" t="inlineStr"/>
-      <c r="I849" t="inlineStr"/>
       <c r="J849" t="n">
         <v>0</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
       </c>
-      <c r="L849" t="inlineStr"/>
       <c r="M849" t="n">
         <v>0</v>
       </c>
@@ -61013,7 +60477,6 @@
       <c r="G850" t="n">
         <v>4</v>
       </c>
-      <c r="H850" t="inlineStr"/>
       <c r="I850" t="inlineStr">
         <is>
           <t>4*</t>
@@ -61230,7 +60693,6 @@
       <c r="G853" t="n">
         <v>2</v>
       </c>
-      <c r="H853" t="inlineStr"/>
       <c r="I853" t="inlineStr">
         <is>
           <t>2*</t>
@@ -61301,7 +60763,6 @@
       <c r="G854" t="n">
         <v>12</v>
       </c>
-      <c r="H854" t="inlineStr"/>
       <c r="I854" t="inlineStr">
         <is>
           <t>12*</t>
@@ -61751,7 +61212,6 @@
       <c r="K860" t="n">
         <v>0</v>
       </c>
-      <c r="L860" t="inlineStr"/>
       <c r="M860" t="n">
         <v>0</v>
       </c>
@@ -61808,15 +61268,12 @@
       <c r="G861" t="n">
         <v>0</v>
       </c>
-      <c r="H861" t="inlineStr"/>
-      <c r="I861" t="inlineStr"/>
       <c r="J861" t="n">
         <v>0</v>
       </c>
       <c r="K861" t="n">
         <v>0</v>
       </c>
-      <c r="L861" t="inlineStr"/>
       <c r="M861" t="n">
         <v>0</v>
       </c>
@@ -61887,7 +61344,6 @@
       <c r="K862" t="n">
         <v>0</v>
       </c>
-      <c r="L862" t="inlineStr"/>
       <c r="M862" t="n">
         <v>0</v>
       </c>
@@ -61944,15 +61400,12 @@
       <c r="G863" t="n">
         <v>0</v>
       </c>
-      <c r="H863" t="inlineStr"/>
-      <c r="I863" t="inlineStr"/>
       <c r="J863" t="n">
         <v>0</v>
       </c>
       <c r="K863" t="n">
         <v>0</v>
       </c>
-      <c r="L863" t="inlineStr"/>
       <c r="M863" t="n">
         <v>0</v>
       </c>
@@ -62023,7 +61476,6 @@
       <c r="K864" t="n">
         <v>0</v>
       </c>
-      <c r="L864" t="inlineStr"/>
       <c r="M864" t="n">
         <v>0</v>
       </c>
@@ -62094,7 +61546,6 @@
       <c r="K865" t="n">
         <v>0</v>
       </c>
-      <c r="L865" t="inlineStr"/>
       <c r="M865" t="n">
         <v>0</v>
       </c>
@@ -62165,7 +61616,6 @@
       <c r="K866" t="n">
         <v>0</v>
       </c>
-      <c r="L866" t="inlineStr"/>
       <c r="M866" t="n">
         <v>0</v>
       </c>
@@ -62236,7 +61686,6 @@
       <c r="K867" t="n">
         <v>0</v>
       </c>
-      <c r="L867" t="inlineStr"/>
       <c r="M867" t="n">
         <v>0</v>
       </c>
@@ -62307,7 +61756,6 @@
       <c r="K868" t="n">
         <v>0</v>
       </c>
-      <c r="L868" t="inlineStr"/>
       <c r="M868" t="n">
         <v>0</v>
       </c>
@@ -62378,7 +61826,6 @@
       <c r="K869" t="n">
         <v>0</v>
       </c>
-      <c r="L869" t="inlineStr"/>
       <c r="M869" t="n">
         <v>0</v>
       </c>
@@ -62449,7 +61896,6 @@
       <c r="K870" t="n">
         <v>0</v>
       </c>
-      <c r="L870" t="inlineStr"/>
       <c r="M870" t="n">
         <v>0</v>
       </c>
@@ -62506,15 +61952,12 @@
       <c r="G871" t="n">
         <v>0</v>
       </c>
-      <c r="H871" t="inlineStr"/>
-      <c r="I871" t="inlineStr"/>
       <c r="J871" t="n">
         <v>0</v>
       </c>
       <c r="K871" t="n">
         <v>0</v>
       </c>
-      <c r="L871" t="inlineStr"/>
       <c r="M871" t="n">
         <v>0</v>
       </c>
@@ -62585,7 +62028,6 @@
       <c r="K872" t="n">
         <v>0</v>
       </c>
-      <c r="L872" t="inlineStr"/>
       <c r="M872" t="n">
         <v>0</v>
       </c>
@@ -62642,7 +62084,6 @@
       <c r="G873" t="n">
         <v>52</v>
       </c>
-      <c r="H873" t="inlineStr"/>
       <c r="I873" t="inlineStr">
         <is>
           <t>52*</t>
@@ -62654,7 +62095,6 @@
       <c r="K873" t="n">
         <v>0</v>
       </c>
-      <c r="L873" t="inlineStr"/>
       <c r="M873" t="n">
         <v>0</v>
       </c>
@@ -62711,7 +62151,6 @@
       <c r="G874" t="n">
         <v>34</v>
       </c>
-      <c r="H874" t="inlineStr"/>
       <c r="I874" t="inlineStr">
         <is>
           <t>34*</t>
@@ -62723,7 +62162,6 @@
       <c r="K874" t="n">
         <v>0</v>
       </c>
-      <c r="L874" t="inlineStr"/>
       <c r="M874" t="n">
         <v>0</v>
       </c>
@@ -62780,7 +62218,6 @@
       <c r="G875" t="n">
         <v>40</v>
       </c>
-      <c r="H875" t="inlineStr"/>
       <c r="I875" t="inlineStr">
         <is>
           <t>40*</t>
@@ -62792,7 +62229,6 @@
       <c r="K875" t="n">
         <v>0</v>
       </c>
-      <c r="L875" t="inlineStr"/>
       <c r="M875" t="n">
         <v>0</v>
       </c>
@@ -62863,7 +62299,6 @@
       <c r="K876" t="n">
         <v>0</v>
       </c>
-      <c r="L876" t="inlineStr"/>
       <c r="M876" t="n">
         <v>0</v>
       </c>
@@ -62934,7 +62369,6 @@
       <c r="K877" t="n">
         <v>0</v>
       </c>
-      <c r="L877" t="inlineStr"/>
       <c r="M877" t="n">
         <v>0</v>
       </c>
@@ -62991,7 +62425,6 @@
       <c r="G878" t="n">
         <v>12</v>
       </c>
-      <c r="H878" t="inlineStr"/>
       <c r="I878" t="inlineStr">
         <is>
           <t>12*</t>
@@ -63003,7 +62436,6 @@
       <c r="K878" t="n">
         <v>0</v>
       </c>
-      <c r="L878" t="inlineStr"/>
       <c r="M878" t="n">
         <v>0</v>
       </c>
@@ -63060,15 +62492,12 @@
       <c r="G879" t="n">
         <v>0</v>
       </c>
-      <c r="H879" t="inlineStr"/>
-      <c r="I879" t="inlineStr"/>
       <c r="J879" t="n">
         <v>0</v>
       </c>
       <c r="K879" t="n">
         <v>0</v>
       </c>
-      <c r="L879" t="inlineStr"/>
       <c r="M879" t="n">
         <v>0</v>
       </c>
@@ -63139,7 +62568,6 @@
       <c r="K880" t="n">
         <v>0</v>
       </c>
-      <c r="L880" t="inlineStr"/>
       <c r="M880" t="n">
         <v>0</v>
       </c>
@@ -63210,7 +62638,6 @@
       <c r="K881" t="n">
         <v>0</v>
       </c>
-      <c r="L881" t="inlineStr"/>
       <c r="M881" t="n">
         <v>0</v>
       </c>
@@ -63559,7 +62986,6 @@
       <c r="G886" t="n">
         <v>8</v>
       </c>
-      <c r="H886" t="inlineStr"/>
       <c r="I886" t="inlineStr">
         <is>
           <t>8*</t>
@@ -64141,15 +63567,12 @@
       <c r="G894" t="n">
         <v>0</v>
       </c>
-      <c r="H894" t="inlineStr"/>
-      <c r="I894" t="inlineStr"/>
       <c r="J894" t="n">
         <v>0</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
       </c>
-      <c r="L894" t="inlineStr"/>
       <c r="M894" t="n">
         <v>0</v>
       </c>
@@ -64279,7 +63702,6 @@
       <c r="G896" t="n">
         <v>2</v>
       </c>
-      <c r="H896" t="inlineStr"/>
       <c r="I896" t="inlineStr">
         <is>
           <t>2*</t>
@@ -64569,7 +63991,6 @@
       <c r="G900" t="n">
         <v>0</v>
       </c>
-      <c r="H900" t="inlineStr"/>
       <c r="I900" t="inlineStr">
         <is>
           <t>0*</t>
@@ -65224,15 +64645,12 @@
       <c r="G909" t="n">
         <v>0</v>
       </c>
-      <c r="H909" t="inlineStr"/>
-      <c r="I909" t="inlineStr"/>
       <c r="J909" t="n">
         <v>0</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
       </c>
-      <c r="L909" t="inlineStr"/>
       <c r="M909" t="n">
         <v>0</v>
       </c>
@@ -65289,7 +64707,6 @@
       <c r="G910" t="n">
         <v>61</v>
       </c>
-      <c r="H910" t="inlineStr"/>
       <c r="I910" t="inlineStr">
         <is>
           <t>61*</t>
@@ -65506,7 +64923,6 @@
       <c r="G913" t="n">
         <v>4</v>
       </c>
-      <c r="H913" t="inlineStr"/>
       <c r="I913" t="inlineStr">
         <is>
           <t>4*</t>
@@ -65577,7 +64993,6 @@
       <c r="G914" t="n">
         <v>1</v>
       </c>
-      <c r="H914" t="inlineStr"/>
       <c r="I914" t="inlineStr">
         <is>
           <t>1*</t>
@@ -65794,15 +65209,12 @@
       <c r="G917" t="n">
         <v>0</v>
       </c>
-      <c r="H917" t="inlineStr"/>
-      <c r="I917" t="inlineStr"/>
       <c r="J917" t="n">
         <v>0</v>
       </c>
       <c r="K917" t="n">
         <v>0</v>
       </c>
-      <c r="L917" t="inlineStr"/>
       <c r="M917" t="n">
         <v>0</v>
       </c>
@@ -65932,15 +65344,12 @@
       <c r="G919" t="n">
         <v>0</v>
       </c>
-      <c r="H919" t="inlineStr"/>
-      <c r="I919" t="inlineStr"/>
       <c r="J919" t="n">
         <v>0</v>
       </c>
       <c r="K919" t="n">
         <v>0</v>
       </c>
-      <c r="L919" t="inlineStr"/>
       <c r="M919" t="n">
         <v>0</v>
       </c>
@@ -66143,7 +65552,6 @@
       <c r="G922" t="n">
         <v>82</v>
       </c>
-      <c r="H922" t="inlineStr"/>
       <c r="I922" t="inlineStr">
         <is>
           <t>82*</t>
@@ -66214,15 +65622,12 @@
       <c r="G923" t="n">
         <v>0</v>
       </c>
-      <c r="H923" t="inlineStr"/>
-      <c r="I923" t="inlineStr"/>
       <c r="J923" t="n">
         <v>0</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
       </c>
-      <c r="L923" t="inlineStr"/>
       <c r="M923" t="n">
         <v>0</v>
       </c>
@@ -66717,15 +66122,12 @@
       <c r="G930" t="n">
         <v>0</v>
       </c>
-      <c r="H930" t="inlineStr"/>
-      <c r="I930" t="inlineStr"/>
       <c r="J930" t="n">
         <v>0</v>
       </c>
       <c r="K930" t="n">
         <v>0</v>
       </c>
-      <c r="L930" t="inlineStr"/>
       <c r="M930" t="n">
         <v>0</v>
       </c>
@@ -66928,15 +66330,12 @@
       <c r="G933" t="n">
         <v>0</v>
       </c>
-      <c r="H933" t="inlineStr"/>
-      <c r="I933" t="inlineStr"/>
       <c r="J933" t="n">
         <v>0</v>
       </c>
       <c r="K933" t="n">
         <v>0</v>
       </c>
-      <c r="L933" t="inlineStr"/>
       <c r="M933" t="n">
         <v>0</v>
       </c>
@@ -67212,15 +66611,12 @@
       <c r="G937" t="n">
         <v>0</v>
       </c>
-      <c r="H937" t="inlineStr"/>
-      <c r="I937" t="inlineStr"/>
       <c r="J937" t="n">
         <v>0</v>
       </c>
       <c r="K937" t="n">
         <v>0</v>
       </c>
-      <c r="L937" t="inlineStr"/>
       <c r="M937" t="n">
         <v>0</v>
       </c>
@@ -67423,7 +66819,6 @@
       <c r="G940" t="n">
         <v>3</v>
       </c>
-      <c r="H940" t="inlineStr"/>
       <c r="I940" t="inlineStr">
         <is>
           <t>3*</t>
@@ -67567,7 +66962,6 @@
       <c r="G942" t="n">
         <v>64</v>
       </c>
-      <c r="H942" t="inlineStr"/>
       <c r="I942" t="inlineStr">
         <is>
           <t>64*</t>
@@ -67711,7 +67105,6 @@
       <c r="G944" t="n">
         <v>24</v>
       </c>
-      <c r="H944" t="inlineStr"/>
       <c r="I944" t="inlineStr">
         <is>
           <t>24*</t>
@@ -67928,15 +67321,12 @@
       <c r="G947" t="n">
         <v>0</v>
       </c>
-      <c r="H947" t="inlineStr"/>
-      <c r="I947" t="inlineStr"/>
       <c r="J947" t="n">
         <v>0</v>
       </c>
       <c r="K947" t="n">
         <v>0</v>
       </c>
-      <c r="L947" t="inlineStr"/>
       <c r="M947" t="n">
         <v>0</v>
       </c>
@@ -68139,7 +67529,6 @@
       <c r="G950" t="n">
         <v>66</v>
       </c>
-      <c r="H950" t="inlineStr"/>
       <c r="I950" t="inlineStr">
         <is>
           <t>66*</t>
@@ -68356,15 +67745,12 @@
       <c r="G953" t="n">
         <v>0</v>
       </c>
-      <c r="H953" t="inlineStr"/>
-      <c r="I953" t="inlineStr"/>
       <c r="J953" t="n">
         <v>0</v>
       </c>
       <c r="K953" t="n">
         <v>0</v>
       </c>
-      <c r="L953" t="inlineStr"/>
       <c r="M953" t="n">
         <v>0</v>
       </c>
@@ -68421,15 +67807,12 @@
       <c r="G954" t="n">
         <v>0</v>
       </c>
-      <c r="H954" t="inlineStr"/>
-      <c r="I954" t="inlineStr"/>
       <c r="J954" t="n">
         <v>0</v>
       </c>
       <c r="K954" t="n">
         <v>0</v>
       </c>
-      <c r="L954" t="inlineStr"/>
       <c r="M954" t="n">
         <v>0</v>
       </c>
@@ -68559,15 +67942,12 @@
       <c r="G956" t="n">
         <v>0</v>
       </c>
-      <c r="H956" t="inlineStr"/>
-      <c r="I956" t="inlineStr"/>
       <c r="J956" t="n">
         <v>0</v>
       </c>
       <c r="K956" t="n">
         <v>0</v>
       </c>
-      <c r="L956" t="inlineStr"/>
       <c r="M956" t="n">
         <v>0</v>
       </c>
@@ -68770,7 +68150,6 @@
       <c r="G959" t="n">
         <v>89</v>
       </c>
-      <c r="H959" t="inlineStr"/>
       <c r="I959" t="inlineStr">
         <is>
           <t>89*</t>
@@ -68914,15 +68293,12 @@
       <c r="G961" t="n">
         <v>0</v>
       </c>
-      <c r="H961" t="inlineStr"/>
-      <c r="I961" t="inlineStr"/>
       <c r="J961" t="n">
         <v>0</v>
       </c>
       <c r="K961" t="n">
         <v>0</v>
       </c>
-      <c r="L961" t="inlineStr"/>
       <c r="M961" t="n">
         <v>0</v>
       </c>
@@ -68979,15 +68355,12 @@
       <c r="G962" t="n">
         <v>0</v>
       </c>
-      <c r="H962" t="inlineStr"/>
-      <c r="I962" t="inlineStr"/>
       <c r="J962" t="n">
         <v>0</v>
       </c>
       <c r="K962" t="n">
         <v>0</v>
       </c>
-      <c r="L962" t="inlineStr"/>
       <c r="M962" t="n">
         <v>0</v>
       </c>
@@ -69117,7 +68490,6 @@
       <c r="G964" t="n">
         <v>8</v>
       </c>
-      <c r="H964" t="inlineStr"/>
       <c r="I964" t="inlineStr">
         <is>
           <t>8*</t>
@@ -69334,15 +68706,12 @@
       <c r="G967" t="n">
         <v>0</v>
       </c>
-      <c r="H967" t="inlineStr"/>
-      <c r="I967" t="inlineStr"/>
       <c r="J967" t="n">
         <v>0</v>
       </c>
       <c r="K967" t="n">
         <v>0</v>
       </c>
-      <c r="L967" t="inlineStr"/>
       <c r="M967" t="n">
         <v>0</v>
       </c>
@@ -69545,15 +68914,12 @@
       <c r="G970" t="n">
         <v>0</v>
       </c>
-      <c r="H970" t="inlineStr"/>
-      <c r="I970" t="inlineStr"/>
       <c r="J970" t="n">
         <v>0</v>
       </c>
       <c r="K970" t="n">
         <v>0</v>
       </c>
-      <c r="L970" t="inlineStr"/>
       <c r="M970" t="n">
         <v>0</v>
       </c>
@@ -69756,7 +69122,6 @@
       <c r="G973" t="n">
         <v>0</v>
       </c>
-      <c r="H973" t="inlineStr"/>
       <c r="I973" t="inlineStr">
         <is>
           <t>0*</t>
@@ -69900,15 +69265,12 @@
       <c r="G975" t="n">
         <v>0</v>
       </c>
-      <c r="H975" t="inlineStr"/>
-      <c r="I975" t="inlineStr"/>
       <c r="J975" t="n">
         <v>0</v>
       </c>
       <c r="K975" t="n">
         <v>0</v>
       </c>
-      <c r="L975" t="inlineStr"/>
       <c r="M975" t="n">
         <v>0</v>
       </c>
@@ -70257,7 +69619,6 @@
       <c r="G980" t="n">
         <v>64</v>
       </c>
-      <c r="H980" t="inlineStr"/>
       <c r="I980" t="inlineStr">
         <is>
           <t>64*</t>
@@ -70328,15 +69689,12 @@
       <c r="G981" t="n">
         <v>0</v>
       </c>
-      <c r="H981" t="inlineStr"/>
-      <c r="I981" t="inlineStr"/>
       <c r="J981" t="n">
         <v>0</v>
       </c>
       <c r="K981" t="n">
         <v>0</v>
       </c>
-      <c r="L981" t="inlineStr"/>
       <c r="M981" t="n">
         <v>0</v>
       </c>
@@ -70466,7 +69824,6 @@
       <c r="G983" t="n">
         <v>22</v>
       </c>
-      <c r="H983" t="inlineStr"/>
       <c r="I983" t="inlineStr">
         <is>
           <t>22*</t>
@@ -70610,15 +69967,12 @@
       <c r="G985" t="n">
         <v>0</v>
       </c>
-      <c r="H985" t="inlineStr"/>
-      <c r="I985" t="inlineStr"/>
       <c r="J985" t="n">
         <v>0</v>
       </c>
       <c r="K985" t="n">
         <v>0</v>
       </c>
-      <c r="L985" t="inlineStr"/>
       <c r="M985" t="n">
         <v>0</v>
       </c>
@@ -70675,15 +70029,12 @@
       <c r="G986" t="n">
         <v>0</v>
       </c>
-      <c r="H986" t="inlineStr"/>
-      <c r="I986" t="inlineStr"/>
       <c r="J986" t="n">
         <v>0</v>
       </c>
       <c r="K986" t="n">
         <v>0</v>
       </c>
-      <c r="L986" t="inlineStr"/>
       <c r="M986" t="n">
         <v>0</v>
       </c>
@@ -70959,15 +70310,12 @@
       <c r="G990" t="n">
         <v>0</v>
       </c>
-      <c r="H990" t="inlineStr"/>
-      <c r="I990" t="inlineStr"/>
       <c r="J990" t="n">
         <v>0</v>
       </c>
       <c r="K990" t="n">
         <v>0</v>
       </c>
-      <c r="L990" t="inlineStr"/>
       <c r="M990" t="n">
         <v>0</v>
       </c>
@@ -71170,15 +70518,12 @@
       <c r="G993" t="n">
         <v>0</v>
       </c>
-      <c r="H993" t="inlineStr"/>
-      <c r="I993" t="inlineStr"/>
       <c r="J993" t="n">
         <v>0</v>
       </c>
       <c r="K993" t="n">
         <v>0</v>
       </c>
-      <c r="L993" t="inlineStr"/>
       <c r="M993" t="n">
         <v>0</v>
       </c>
@@ -71235,15 +70580,12 @@
       <c r="G994" t="n">
         <v>0</v>
       </c>
-      <c r="H994" t="inlineStr"/>
-      <c r="I994" t="inlineStr"/>
       <c r="J994" t="n">
         <v>0</v>
       </c>
       <c r="K994" t="n">
         <v>0</v>
       </c>
-      <c r="L994" t="inlineStr"/>
       <c r="M994" t="n">
         <v>0</v>
       </c>
@@ -71373,7 +70715,6 @@
       <c r="G996" t="n">
         <v>6</v>
       </c>
-      <c r="H996" t="inlineStr"/>
       <c r="I996" t="inlineStr">
         <is>
           <t>6*</t>
@@ -71444,15 +70785,12 @@
       <c r="G997" t="n">
         <v>0</v>
       </c>
-      <c r="H997" t="inlineStr"/>
-      <c r="I997" t="inlineStr"/>
       <c r="J997" t="n">
         <v>0</v>
       </c>
       <c r="K997" t="n">
         <v>0</v>
       </c>
-      <c r="L997" t="inlineStr"/>
       <c r="M997" t="n">
         <v>0</v>
       </c>
@@ -71509,7 +70847,6 @@
       <c r="G998" t="n">
         <v>3</v>
       </c>
-      <c r="H998" t="inlineStr"/>
       <c r="I998" t="inlineStr">
         <is>
           <t>3*</t>
@@ -71872,7 +71209,6 @@
       <c r="G1003" t="n">
         <v>2</v>
       </c>
-      <c r="H1003" t="inlineStr"/>
       <c r="I1003" t="inlineStr">
         <is>
           <t>2*</t>
@@ -72308,15 +71644,12 @@
       <c r="G1009" t="n">
         <v>0</v>
       </c>
-      <c r="H1009" t="inlineStr"/>
-      <c r="I1009" t="inlineStr"/>
       <c r="J1009" t="n">
         <v>0</v>
       </c>
       <c r="K1009" t="n">
         <v>0</v>
       </c>
-      <c r="L1009" t="inlineStr"/>
       <c r="M1009" t="n">
         <v>0</v>
       </c>
@@ -72373,7 +71706,6 @@
       <c r="G1010" t="n">
         <v>2</v>
       </c>
-      <c r="H1010" t="inlineStr"/>
       <c r="I1010" t="inlineStr">
         <is>
           <t>2*</t>
@@ -72590,15 +71922,12 @@
       <c r="G1013" t="n">
         <v>0</v>
       </c>
-      <c r="H1013" t="inlineStr"/>
-      <c r="I1013" t="inlineStr"/>
       <c r="J1013" t="n">
         <v>0</v>
       </c>
       <c r="K1013" t="n">
         <v>0</v>
       </c>
-      <c r="L1013" t="inlineStr"/>
       <c r="M1013" t="n">
         <v>0</v>
       </c>
@@ -72655,15 +71984,12 @@
       <c r="G1014" t="n">
         <v>0</v>
       </c>
-      <c r="H1014" t="inlineStr"/>
-      <c r="I1014" t="inlineStr"/>
       <c r="J1014" t="n">
         <v>0</v>
       </c>
       <c r="K1014" t="n">
         <v>0</v>
       </c>
-      <c r="L1014" t="inlineStr"/>
       <c r="M1014" t="n">
         <v>0</v>
       </c>
@@ -72866,15 +72192,12 @@
       <c r="G1017" t="n">
         <v>0</v>
       </c>
-      <c r="H1017" t="inlineStr"/>
-      <c r="I1017" t="inlineStr"/>
       <c r="J1017" t="n">
         <v>0</v>
       </c>
       <c r="K1017" t="n">
         <v>0</v>
       </c>
-      <c r="L1017" t="inlineStr"/>
       <c r="M1017" t="n">
         <v>0</v>
       </c>
@@ -73004,7 +72327,6 @@
       <c r="G1019" t="n">
         <v>3</v>
       </c>
-      <c r="H1019" t="inlineStr"/>
       <c r="I1019" t="inlineStr">
         <is>
           <t>3*</t>
@@ -73148,15 +72470,12 @@
       <c r="G1021" t="n">
         <v>0</v>
       </c>
-      <c r="H1021" t="inlineStr"/>
-      <c r="I1021" t="inlineStr"/>
       <c r="J1021" t="n">
         <v>0</v>
       </c>
       <c r="K1021" t="n">
         <v>0</v>
       </c>
-      <c r="L1021" t="inlineStr"/>
       <c r="M1021" t="n">
         <v>0</v>
       </c>
@@ -73213,15 +72532,12 @@
       <c r="G1022" t="n">
         <v>0</v>
       </c>
-      <c r="H1022" t="inlineStr"/>
-      <c r="I1022" t="inlineStr"/>
       <c r="J1022" t="n">
         <v>0</v>
       </c>
       <c r="K1022" t="n">
         <v>0</v>
       </c>
-      <c r="L1022" t="inlineStr"/>
       <c r="M1022" t="n">
         <v>0</v>
       </c>
@@ -73351,15 +72667,12 @@
       <c r="G1024" t="n">
         <v>0</v>
       </c>
-      <c r="H1024" t="inlineStr"/>
-      <c r="I1024" t="inlineStr"/>
       <c r="J1024" t="n">
         <v>0</v>
       </c>
       <c r="K1024" t="n">
         <v>0</v>
       </c>
-      <c r="L1024" t="inlineStr"/>
       <c r="M1024" t="n">
         <v>0</v>
       </c>
@@ -73416,7 +72729,6 @@
       <c r="G1025" t="n">
         <v>29</v>
       </c>
-      <c r="H1025" t="inlineStr"/>
       <c r="I1025" t="inlineStr">
         <is>
           <t>29*</t>
@@ -73633,15 +72945,12 @@
       <c r="G1028" t="n">
         <v>0</v>
       </c>
-      <c r="H1028" t="inlineStr"/>
-      <c r="I1028" t="inlineStr"/>
       <c r="J1028" t="n">
         <v>0</v>
       </c>
       <c r="K1028" t="n">
         <v>0</v>
       </c>
-      <c r="L1028" t="inlineStr"/>
       <c r="M1028" t="n">
         <v>0</v>
       </c>
@@ -73771,15 +73080,12 @@
       <c r="G1030" t="n">
         <v>0</v>
       </c>
-      <c r="H1030" t="inlineStr"/>
-      <c r="I1030" t="inlineStr"/>
       <c r="J1030" t="n">
         <v>0</v>
       </c>
       <c r="K1030" t="n">
         <v>0</v>
       </c>
-      <c r="L1030" t="inlineStr"/>
       <c r="M1030" t="n">
         <v>0</v>
       </c>
@@ -73836,7 +73142,6 @@
       <c r="G1031" t="n">
         <v>13</v>
       </c>
-      <c r="H1031" t="inlineStr"/>
       <c r="I1031" t="inlineStr">
         <is>
           <t>13*</t>
@@ -74491,7 +73796,6 @@
       <c r="G1040" t="n">
         <v>22</v>
       </c>
-      <c r="H1040" t="inlineStr"/>
       <c r="I1040" t="inlineStr">
         <is>
           <t>22*</t>
@@ -75000,7 +74304,6 @@
       <c r="G1047" t="n">
         <v>1</v>
       </c>
-      <c r="H1047" t="inlineStr"/>
       <c r="I1047" t="inlineStr">
         <is>
           <t>1*</t>
@@ -75217,15 +74520,12 @@
       <c r="G1050" t="n">
         <v>0</v>
       </c>
-      <c r="H1050" t="inlineStr"/>
-      <c r="I1050" t="inlineStr"/>
       <c r="J1050" t="n">
         <v>0</v>
       </c>
       <c r="K1050" t="n">
         <v>0</v>
       </c>
-      <c r="L1050" t="inlineStr"/>
       <c r="M1050" t="n">
         <v>0</v>
       </c>
@@ -75282,7 +74582,6 @@
       <c r="G1051" t="n">
         <v>5</v>
       </c>
-      <c r="H1051" t="inlineStr"/>
       <c r="I1051" t="inlineStr">
         <is>
           <t>5*</t>
@@ -75864,15 +75163,12 @@
       <c r="G1059" t="n">
         <v>0</v>
       </c>
-      <c r="H1059" t="inlineStr"/>
-      <c r="I1059" t="inlineStr"/>
       <c r="J1059" t="n">
         <v>0</v>
       </c>
       <c r="K1059" t="n">
         <v>0</v>
       </c>
-      <c r="L1059" t="inlineStr"/>
       <c r="M1059" t="n">
         <v>0</v>
       </c>
@@ -75929,15 +75225,12 @@
       <c r="G1060" t="n">
         <v>0</v>
       </c>
-      <c r="H1060" t="inlineStr"/>
-      <c r="I1060" t="inlineStr"/>
       <c r="J1060" t="n">
         <v>0</v>
       </c>
       <c r="K1060" t="n">
         <v>0</v>
       </c>
-      <c r="L1060" t="inlineStr"/>
       <c r="M1060" t="n">
         <v>0</v>
       </c>
@@ -76067,15 +75360,12 @@
       <c r="G1062" t="n">
         <v>0</v>
       </c>
-      <c r="H1062" t="inlineStr"/>
-      <c r="I1062" t="inlineStr"/>
       <c r="J1062" t="n">
         <v>0</v>
       </c>
       <c r="K1062" t="n">
         <v>0</v>
       </c>
-      <c r="L1062" t="inlineStr"/>
       <c r="M1062" t="n">
         <v>0</v>
       </c>
@@ -76132,15 +75422,12 @@
       <c r="G1063" t="n">
         <v>0</v>
       </c>
-      <c r="H1063" t="inlineStr"/>
-      <c r="I1063" t="inlineStr"/>
       <c r="J1063" t="n">
         <v>0</v>
       </c>
       <c r="K1063" t="n">
         <v>0</v>
       </c>
-      <c r="L1063" t="inlineStr"/>
       <c r="M1063" t="n">
         <v>0</v>
       </c>
@@ -76197,15 +75484,12 @@
       <c r="G1064" t="n">
         <v>0</v>
       </c>
-      <c r="H1064" t="inlineStr"/>
-      <c r="I1064" t="inlineStr"/>
       <c r="J1064" t="n">
         <v>0</v>
       </c>
       <c r="K1064" t="n">
         <v>0</v>
       </c>
-      <c r="L1064" t="inlineStr"/>
       <c r="M1064" t="n">
         <v>0</v>
       </c>
@@ -76262,15 +75546,12 @@
       <c r="G1065" t="n">
         <v>0</v>
       </c>
-      <c r="H1065" t="inlineStr"/>
-      <c r="I1065" t="inlineStr"/>
       <c r="J1065" t="n">
         <v>0</v>
       </c>
       <c r="K1065" t="n">
         <v>0</v>
       </c>
-      <c r="L1065" t="inlineStr"/>
       <c r="M1065" t="n">
         <v>0</v>
       </c>
@@ -76327,15 +75608,12 @@
       <c r="G1066" t="n">
         <v>0</v>
       </c>
-      <c r="H1066" t="inlineStr"/>
-      <c r="I1066" t="inlineStr"/>
       <c r="J1066" t="n">
         <v>0</v>
       </c>
       <c r="K1066" t="n">
         <v>0</v>
       </c>
-      <c r="L1066" t="inlineStr"/>
       <c r="M1066" t="n">
         <v>0</v>
       </c>
@@ -76392,7 +75670,6 @@
       <c r="G1067" t="n">
         <v>1</v>
       </c>
-      <c r="H1067" t="inlineStr"/>
       <c r="I1067" t="inlineStr">
         <is>
           <t>1*</t>
@@ -76536,15 +75813,12 @@
       <c r="G1069" t="n">
         <v>0</v>
       </c>
-      <c r="H1069" t="inlineStr"/>
-      <c r="I1069" t="inlineStr"/>
       <c r="J1069" t="n">
         <v>0</v>
       </c>
       <c r="K1069" t="n">
         <v>0</v>
       </c>
-      <c r="L1069" t="inlineStr"/>
       <c r="M1069" t="n">
         <v>0</v>
       </c>
@@ -76601,15 +75875,12 @@
       <c r="G1070" t="n">
         <v>0</v>
       </c>
-      <c r="H1070" t="inlineStr"/>
-      <c r="I1070" t="inlineStr"/>
       <c r="J1070" t="n">
         <v>0</v>
       </c>
       <c r="K1070" t="n">
         <v>0</v>
       </c>
-      <c r="L1070" t="inlineStr"/>
       <c r="M1070" t="n">
         <v>0</v>
       </c>
@@ -76666,15 +75937,12 @@
       <c r="G1071" t="n">
         <v>0</v>
       </c>
-      <c r="H1071" t="inlineStr"/>
-      <c r="I1071" t="inlineStr"/>
       <c r="J1071" t="n">
         <v>0</v>
       </c>
       <c r="K1071" t="n">
         <v>0</v>
       </c>
-      <c r="L1071" t="inlineStr"/>
       <c r="M1071" t="n">
         <v>0</v>
       </c>
@@ -76731,15 +75999,12 @@
       <c r="G1072" t="n">
         <v>0</v>
       </c>
-      <c r="H1072" t="inlineStr"/>
-      <c r="I1072" t="inlineStr"/>
       <c r="J1072" t="n">
         <v>0</v>
       </c>
       <c r="K1072" t="n">
         <v>0</v>
       </c>
-      <c r="L1072" t="inlineStr"/>
       <c r="M1072" t="n">
         <v>0</v>
       </c>
@@ -76942,15 +76207,12 @@
       <c r="G1075" t="n">
         <v>0</v>
       </c>
-      <c r="H1075" t="inlineStr"/>
-      <c r="I1075" t="inlineStr"/>
       <c r="J1075" t="n">
         <v>0</v>
       </c>
       <c r="K1075" t="n">
         <v>0</v>
       </c>
-      <c r="L1075" t="inlineStr"/>
       <c r="M1075" t="n">
         <v>0</v>
       </c>
@@ -77007,15 +76269,12 @@
       <c r="G1076" t="n">
         <v>0</v>
       </c>
-      <c r="H1076" t="inlineStr"/>
-      <c r="I1076" t="inlineStr"/>
       <c r="J1076" t="n">
         <v>0</v>
       </c>
       <c r="K1076" t="n">
         <v>0</v>
       </c>
-      <c r="L1076" t="inlineStr"/>
       <c r="M1076" t="n">
         <v>0</v>
       </c>
@@ -77145,7 +76404,6 @@
       <c r="G1078" t="n">
         <v>36</v>
       </c>
-      <c r="H1078" t="inlineStr"/>
       <c r="I1078" t="inlineStr">
         <is>
           <t>36*</t>
@@ -77216,7 +76474,6 @@
       <c r="G1079" t="n">
         <v>29</v>
       </c>
-      <c r="H1079" t="inlineStr"/>
       <c r="I1079" t="inlineStr">
         <is>
           <t>29*</t>
@@ -77360,15 +76617,12 @@
       <c r="G1081" t="n">
         <v>0</v>
       </c>
-      <c r="H1081" t="inlineStr"/>
-      <c r="I1081" t="inlineStr"/>
       <c r="J1081" t="n">
         <v>0</v>
       </c>
       <c r="K1081" t="n">
         <v>0</v>
       </c>
-      <c r="L1081" t="inlineStr"/>
       <c r="M1081" t="n">
         <v>0</v>
       </c>
@@ -77498,7 +76752,6 @@
       <c r="G1083" t="n">
         <v>24</v>
       </c>
-      <c r="H1083" t="inlineStr"/>
       <c r="I1083" t="inlineStr">
         <is>
           <t>24*</t>
@@ -77715,7 +76968,6 @@
       <c r="G1086" t="n">
         <v>16</v>
       </c>
-      <c r="H1086" t="inlineStr"/>
       <c r="I1086" t="inlineStr">
         <is>
           <t>16*</t>
@@ -78297,7 +77549,6 @@
       <c r="G1094" t="n">
         <v>28</v>
       </c>
-      <c r="H1094" t="inlineStr"/>
       <c r="I1094" t="inlineStr">
         <is>
           <t>28*</t>
@@ -78587,15 +77838,12 @@
       <c r="G1098" t="n">
         <v>0</v>
       </c>
-      <c r="H1098" t="inlineStr"/>
-      <c r="I1098" t="inlineStr"/>
       <c r="J1098" t="n">
         <v>0</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
       </c>
-      <c r="L1098" t="inlineStr"/>
       <c r="M1098" t="n">
         <v>0</v>
       </c>
@@ -79090,15 +78338,12 @@
       <c r="G1105" t="n">
         <v>0</v>
       </c>
-      <c r="H1105" t="inlineStr"/>
-      <c r="I1105" t="inlineStr"/>
       <c r="J1105" t="n">
         <v>0</v>
       </c>
       <c r="K1105" t="n">
         <v>0</v>
       </c>
-      <c r="L1105" t="inlineStr"/>
       <c r="M1105" t="n">
         <v>0</v>
       </c>
@@ -79301,7 +78546,6 @@
       <c r="G1108" t="n">
         <v>15</v>
       </c>
-      <c r="H1108" t="inlineStr"/>
       <c r="I1108" t="inlineStr">
         <is>
           <t>15*</t>
@@ -79518,15 +78762,12 @@
       <c r="G1111" t="n">
         <v>0</v>
       </c>
-      <c r="H1111" t="inlineStr"/>
-      <c r="I1111" t="inlineStr"/>
       <c r="J1111" t="n">
         <v>0</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
       </c>
-      <c r="L1111" t="inlineStr"/>
       <c r="M1111" t="n">
         <v>0</v>
       </c>
@@ -79656,7 +78897,6 @@
       <c r="G1113" t="n">
         <v>6</v>
       </c>
-      <c r="H1113" t="inlineStr"/>
       <c r="I1113" t="inlineStr">
         <is>
           <t>6*</t>
@@ -79727,15 +78967,12 @@
       <c r="G1114" t="n">
         <v>0</v>
       </c>
-      <c r="H1114" t="inlineStr"/>
-      <c r="I1114" t="inlineStr"/>
       <c r="J1114" t="n">
         <v>0</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
       </c>
-      <c r="L1114" t="inlineStr"/>
       <c r="M1114" t="n">
         <v>0</v>
       </c>
@@ -79865,15 +79102,12 @@
       <c r="G1116" t="n">
         <v>0</v>
       </c>
-      <c r="H1116" t="inlineStr"/>
-      <c r="I1116" t="inlineStr"/>
       <c r="J1116" t="n">
         <v>0</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
       </c>
-      <c r="L1116" t="inlineStr"/>
       <c r="M1116" t="n">
         <v>0</v>
       </c>
@@ -79930,15 +79164,12 @@
       <c r="G1117" t="n">
         <v>0</v>
       </c>
-      <c r="H1117" t="inlineStr"/>
-      <c r="I1117" t="inlineStr"/>
       <c r="J1117" t="n">
         <v>0</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
       </c>
-      <c r="L1117" t="inlineStr"/>
       <c r="M1117" t="n">
         <v>0</v>
       </c>
@@ -80141,7 +79372,6 @@
       <c r="G1120" t="n">
         <v>0</v>
       </c>
-      <c r="H1120" t="inlineStr"/>
       <c r="I1120" t="inlineStr">
         <is>
           <t>0*</t>
